--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\iptfiles\EN\LGE\operacao\Areas\CEM\André\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBBDD33D-BD08-4F94-9247-0FB49D58F930}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEEFA225-5ABB-4E47-9591-26BF956A3586}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{52AA075D-27AB-4F9B-8F0B-5CEFB61057CE}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="207">
   <si>
     <t>Nome Equipamento</t>
   </si>
@@ -238,6 +238,414 @@
   </si>
   <si>
     <t>Resistor de 10M Ω</t>
+  </si>
+  <si>
+    <t>6,8 Ω</t>
+  </si>
+  <si>
+    <t>8,2 Ω</t>
+  </si>
+  <si>
+    <t>10 Ω</t>
+  </si>
+  <si>
+    <t>15 Ω</t>
+  </si>
+  <si>
+    <t>18 Ω</t>
+  </si>
+  <si>
+    <t>22 Ω</t>
+  </si>
+  <si>
+    <t>33 Ω</t>
+  </si>
+  <si>
+    <t>47 Ω</t>
+  </si>
+  <si>
+    <t>56 Ω</t>
+  </si>
+  <si>
+    <t>63 Ω</t>
+  </si>
+  <si>
+    <t>68 Ω</t>
+  </si>
+  <si>
+    <t>82 Ω</t>
+  </si>
+  <si>
+    <t>100 Ω</t>
+  </si>
+  <si>
+    <t>120 Ω</t>
+  </si>
+  <si>
+    <t>150 Ω</t>
+  </si>
+  <si>
+    <t>220 Ω</t>
+  </si>
+  <si>
+    <t>270 Ω</t>
+  </si>
+  <si>
+    <t>330 Ω</t>
+  </si>
+  <si>
+    <t>470 Ω</t>
+  </si>
+  <si>
+    <t>680 Ω</t>
+  </si>
+  <si>
+    <t>1 kΩ</t>
+  </si>
+  <si>
+    <t>12 kΩ</t>
+  </si>
+  <si>
+    <t>15 kΩ</t>
+  </si>
+  <si>
+    <t>2,2 kΩ</t>
+  </si>
+  <si>
+    <t>4k7Ω</t>
+  </si>
+  <si>
+    <t>100 kΩ</t>
+  </si>
+  <si>
+    <t>120 kΩ</t>
+  </si>
+  <si>
+    <t>150 kΩ</t>
+  </si>
+  <si>
+    <t>1M Ω</t>
+  </si>
+  <si>
+    <t>47k Ω</t>
+  </si>
+  <si>
+    <t>10M  Ω</t>
+  </si>
+  <si>
+    <t>SLOT B3</t>
+  </si>
+  <si>
+    <t>SLOT B4</t>
+  </si>
+  <si>
+    <t>SLOT B5</t>
+  </si>
+  <si>
+    <t>SLOT B6</t>
+  </si>
+  <si>
+    <t>SLOT B7</t>
+  </si>
+  <si>
+    <t>SLOT B8</t>
+  </si>
+  <si>
+    <t>SLOT C1</t>
+  </si>
+  <si>
+    <t>SLOT C2</t>
+  </si>
+  <si>
+    <t>SLOT C3</t>
+  </si>
+  <si>
+    <t>SLOT C4</t>
+  </si>
+  <si>
+    <t>SLOT C5</t>
+  </si>
+  <si>
+    <t>SLOT C6</t>
+  </si>
+  <si>
+    <t>SLOT C7</t>
+  </si>
+  <si>
+    <t>SLOT C8</t>
+  </si>
+  <si>
+    <t>SLOT D1</t>
+  </si>
+  <si>
+    <t>SLOT D2</t>
+  </si>
+  <si>
+    <t>SLOT D3</t>
+  </si>
+  <si>
+    <t>SLOT D4</t>
+  </si>
+  <si>
+    <t>SLOT D5</t>
+  </si>
+  <si>
+    <t>SLOT D6</t>
+  </si>
+  <si>
+    <t>SLOT D7</t>
+  </si>
+  <si>
+    <t>SLOT D8</t>
+  </si>
+  <si>
+    <t>SLOT E1</t>
+  </si>
+  <si>
+    <t>SLOT E2</t>
+  </si>
+  <si>
+    <t>SLOT E3</t>
+  </si>
+  <si>
+    <t>SLOT E4</t>
+  </si>
+  <si>
+    <t>SLOT E5</t>
+  </si>
+  <si>
+    <t>SLOT E6</t>
+  </si>
+  <si>
+    <t>SLOT E7</t>
+  </si>
+  <si>
+    <t>SLOT E8</t>
+  </si>
+  <si>
+    <t>SLOT F1</t>
+  </si>
+  <si>
+    <t>Capacitor de 1 pF</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>Capacitor de 10 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 15 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 100 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 150 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 820 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 1000 pF</t>
+  </si>
+  <si>
+    <t>Capacitor de 2,2 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 4,7 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 8,2 n F</t>
+  </si>
+  <si>
+    <t>Capacitor 47 nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor de 6,8 nF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor de 10 nF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor de 15 nF </t>
+  </si>
+  <si>
+    <t>Capacitor de 680 nF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor de 0,47 uF </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacitor de 1 uF </t>
+  </si>
+  <si>
+    <t>Capacitor de 2,2 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 22 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 47 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 1000 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 2200 uF</t>
+  </si>
+  <si>
+    <t>1 pF</t>
+  </si>
+  <si>
+    <t>10 pF</t>
+  </si>
+  <si>
+    <t>15 pF</t>
+  </si>
+  <si>
+    <t>100 pF</t>
+  </si>
+  <si>
+    <t>150 pF</t>
+  </si>
+  <si>
+    <t>820 pF</t>
+  </si>
+  <si>
+    <t>1000 pF</t>
+  </si>
+  <si>
+    <t>2 nF</t>
+  </si>
+  <si>
+    <t>7 nF</t>
+  </si>
+  <si>
+    <t>8 nF</t>
+  </si>
+  <si>
+    <t>2 n F</t>
+  </si>
+  <si>
+    <t>10 nF</t>
+  </si>
+  <si>
+    <t>15 nF</t>
+  </si>
+  <si>
+    <t>47 nF</t>
+  </si>
+  <si>
+    <t>680 nF</t>
+  </si>
+  <si>
+    <t>47 uF</t>
+  </si>
+  <si>
+    <t>1 uF</t>
+  </si>
+  <si>
+    <t>2 uF</t>
+  </si>
+  <si>
+    <t>22 uF</t>
+  </si>
+  <si>
+    <t>1000 uF</t>
+  </si>
+  <si>
+    <t>2200 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 10 uF</t>
+  </si>
+  <si>
+    <t>10 uF</t>
+  </si>
+  <si>
+    <t>Varistor</t>
+  </si>
+  <si>
+    <t>Varistor de varios modelos</t>
+  </si>
+  <si>
+    <t>Varios tipos - Favor olhar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caixa de capacitores </t>
+  </si>
+  <si>
+    <t>SLOT A1</t>
+  </si>
+  <si>
+    <t>SLOT A2</t>
+  </si>
+  <si>
+    <t>Capacitor de 1500 uF</t>
+  </si>
+  <si>
+    <t>1500 uF</t>
+  </si>
+  <si>
+    <t>Diversos eletrolíticos</t>
+  </si>
+  <si>
+    <t>Slot D2</t>
+  </si>
+  <si>
+    <t>150 uF</t>
+  </si>
+  <si>
+    <t>Capacitor de 150 uF</t>
+  </si>
+  <si>
+    <t>Capacitor eletrolítico</t>
+  </si>
+  <si>
+    <t>Capacitor de ceramica</t>
+  </si>
+  <si>
+    <t>Capacitor de 33 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 150 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 683 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 22 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 470 nF</t>
+  </si>
+  <si>
+    <t>Capacitor de 560 nF</t>
+  </si>
+  <si>
+    <t>33 nF</t>
+  </si>
+  <si>
+    <t>150 nF</t>
+  </si>
+  <si>
+    <t>683 nF</t>
+  </si>
+  <si>
+    <t>22 nF</t>
+  </si>
+  <si>
+    <t>470 nF</t>
+  </si>
+  <si>
+    <t>560 nF</t>
+  </si>
+  <si>
+    <t>Outros capacitores de cerâmica</t>
+  </si>
+  <si>
+    <t>Slot D3 Diversos ceramica</t>
   </si>
 </sst>
 </file>
@@ -253,22 +661,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0099CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -277,33 +710,63 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -312,6 +775,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF0099CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -620,598 +1088,1727 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAFFE1C-1227-4168-9582-491BF80477F1}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="33.85546875" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+    </row>
+    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>12</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>12</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="3">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="D10" s="4">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="4">
         <v>4</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="B12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>10</v>
+      <c r="B13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="4">
+        <v>10</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>10</v>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="4">
+        <v>96</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>10</v>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D15" s="4">
+        <v>15</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="4">
+        <v>12</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="4">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="4">
         <v>47</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="E19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="4">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="4">
+        <v>9</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="4">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="4">
+        <v>17</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="4">
+        <v>82</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="4">
+        <v>16</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="4">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="4">
+        <v>2</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B29" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="4">
+        <v>4</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B30" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="4">
+        <v>110</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B31" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="4">
+        <v>19</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B32" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="4">
+        <v>98</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B33" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="4">
+        <v>57</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B34" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="4">
+        <v>36</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="4">
+        <v>107</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B36" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B37" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="4">
+        <v>49</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B38" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="4">
+        <v>41</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="4">
+        <v>50</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B40" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D40" s="4">
+        <v>19</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B41" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D41" s="4">
+        <v>22</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B42" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" s="4">
+        <v>45</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>10</v>
+      <c r="B43" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="4">
+        <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="8">
+        <v>119</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="8">
+        <v>50</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" s="8">
+        <v>15</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="8">
+        <v>52</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="8">
+        <v>2</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D49" s="8">
+        <v>6</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D50" s="8">
+        <v>85</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D51" s="8">
+        <v>55</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" s="8">
+        <v>119</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" s="8">
+        <v>2</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="8">
+        <v>2</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D55" s="8">
+        <v>58</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="8">
+        <v>1</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D57" s="8">
+        <v>4</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D58" s="8">
+        <v>1</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D59" s="8">
+        <v>50</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D60" s="8">
+        <v>55</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D61" s="8">
+        <v>53</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="8">
+        <v>19</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D63" s="8">
+        <v>4</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D64" s="8">
+        <v>70</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D65" s="8">
+        <v>14</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D66" s="8">
+        <v>1</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D67" s="8">
+        <v>49</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68" s="8">
+        <v>1</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="8">
+        <v>1</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D70" s="8">
+        <v>1</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="8">
+        <v>1</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D72" s="8">
+        <v>1</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D73" s="8">
+        <v>1</v>
+      </c>
+      <c r="E73" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D74" s="8">
+        <v>1</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="8" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D75" s="8">
+        <v>1</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\André Luis\OneDrive\Ambiente de Trabalho\Documentos\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEEFA225-5ABB-4E47-9591-26BF956A3586}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{52AA075D-27AB-4F9B-8F0B-5CEFB61057CE}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="321">
   <si>
     <t>Nome Equipamento</t>
   </si>
@@ -646,12 +645,354 @@
   </si>
   <si>
     <t>Slot D3 Diversos ceramica</t>
+  </si>
+  <si>
+    <t>Itens para placa</t>
+  </si>
+  <si>
+    <t>Barra de pino 90º Grande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barra de pino reta grande </t>
+  </si>
+  <si>
+    <t>Barra reta p/ CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barra de pino </t>
+  </si>
+  <si>
+    <t>Born KRE 3 vias</t>
+  </si>
+  <si>
+    <t>Born KRE</t>
+  </si>
+  <si>
+    <t>Born KRE 2 vias</t>
+  </si>
+  <si>
+    <t>KIT ANTI ESTATICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caixa dos itens para placa </t>
+  </si>
+  <si>
+    <t>Slot X</t>
+  </si>
+  <si>
+    <t>Caixa dos conectores</t>
+  </si>
+  <si>
+    <t>Botão 2 estágios</t>
+  </si>
+  <si>
+    <t>Botão grande Preto</t>
+  </si>
+  <si>
+    <t>Botão alavanca preto grande</t>
+  </si>
+  <si>
+    <t>Botão Alavanca pequena</t>
+  </si>
+  <si>
+    <t>Plug banana 61 pino</t>
+  </si>
+  <si>
+    <t>Capa de plastico do pino banana</t>
+  </si>
+  <si>
+    <t>Conectores DB25</t>
+  </si>
+  <si>
+    <t>Conector DB9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conector Centronic </t>
+  </si>
+  <si>
+    <t>Conector PLUG</t>
+  </si>
+  <si>
+    <t>Conector born TPR</t>
+  </si>
+  <si>
+    <t>Conector WEG de 3 vias</t>
+  </si>
+  <si>
+    <t>Conector weg de 2 vias</t>
+  </si>
+  <si>
+    <t>Conector de pilha AA</t>
+  </si>
+  <si>
+    <t>Conector de bateria 9v</t>
+  </si>
+  <si>
+    <t>Cabo conector USB positivo e negativo</t>
+  </si>
+  <si>
+    <t>Botão</t>
+  </si>
+  <si>
+    <t>Conectores</t>
+  </si>
+  <si>
+    <t>Conector</t>
+  </si>
+  <si>
+    <t>Plug Banana</t>
+  </si>
+  <si>
+    <t>Slot A</t>
+  </si>
+  <si>
+    <t>Caixa de baterias e pilhas</t>
+  </si>
+  <si>
+    <t>Slot 1</t>
+  </si>
+  <si>
+    <t>Suporte de pilha AA</t>
+  </si>
+  <si>
+    <t>Suporte de pilha de lítio 2032</t>
+  </si>
+  <si>
+    <t>Suporte de pilha de bateria de 9v</t>
+  </si>
+  <si>
+    <t>Baterias de lítio 2032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suporte de pilha </t>
+  </si>
+  <si>
+    <t>Suporte de Bateria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bateria </t>
+  </si>
+  <si>
+    <t>Baterias e pilhas e suportes</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Led BRIGHT BQ-N284RD</t>
+  </si>
+  <si>
+    <t>Led BRIGHT BQN28GERD</t>
+  </si>
+  <si>
+    <t>DISPLAY LED A-551E</t>
+  </si>
+  <si>
+    <t>DISPLAY LED OPD5423SR3MCGW-A1</t>
+  </si>
+  <si>
+    <t>Caixa dos displays</t>
+  </si>
+  <si>
+    <t>Displays</t>
+  </si>
+  <si>
+    <t>Caixa dos relés</t>
+  </si>
+  <si>
+    <t>AZ820-2c48de</t>
+  </si>
+  <si>
+    <t>PE014005</t>
+  </si>
+  <si>
+    <t>SRD12VDCs2c</t>
+  </si>
+  <si>
+    <t>G-j-sh-1 1 2l</t>
+  </si>
+  <si>
+    <t>JHV15K1a1b 12Vcc</t>
+  </si>
+  <si>
+    <t>24VJE12v41D</t>
+  </si>
+  <si>
+    <t>svdchf2f/005-s</t>
+  </si>
+  <si>
+    <t>Relé 5 V</t>
+  </si>
+  <si>
+    <t>Relé</t>
+  </si>
+  <si>
+    <t>Protoboard</t>
+  </si>
+  <si>
+    <t>Caixa de protoboard preta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protoboard média </t>
+  </si>
+  <si>
+    <t>Protoboard pequena</t>
+  </si>
+  <si>
+    <t>Protoboard pequena p/ esp32</t>
+  </si>
+  <si>
+    <t>Protoboard Gigante de mais de 2 mil furos</t>
+  </si>
+  <si>
+    <t>Protoboard Grande</t>
+  </si>
+  <si>
+    <t>Protoboard media com pino banana</t>
+  </si>
+  <si>
+    <t>Regulador de tensão</t>
+  </si>
+  <si>
+    <t>L7809</t>
+  </si>
+  <si>
+    <t>SD73818</t>
+  </si>
+  <si>
+    <t>LM7912</t>
+  </si>
+  <si>
+    <t>LM7812</t>
+  </si>
+  <si>
+    <t>LM7805</t>
+  </si>
+  <si>
+    <t>Caixa de reguladores de tensão</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão  L7809</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão SD73818</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão LM7912</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão LM7812</t>
+  </si>
+  <si>
+    <t>Regulador de Tensão LM7805</t>
+  </si>
+  <si>
+    <t>Fusíveis</t>
+  </si>
+  <si>
+    <t>Fusível</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 mA </t>
+  </si>
+  <si>
+    <t>1 A</t>
+  </si>
+  <si>
+    <t>2 A</t>
+  </si>
+  <si>
+    <t>500 mA</t>
+  </si>
+  <si>
+    <t>160 mA</t>
+  </si>
+  <si>
+    <t>6 A</t>
+  </si>
+  <si>
+    <t>20 A</t>
+  </si>
+  <si>
+    <t>5 A</t>
+  </si>
+  <si>
+    <t>10 A</t>
+  </si>
+  <si>
+    <t>800 mA</t>
+  </si>
+  <si>
+    <t>15 A</t>
+  </si>
+  <si>
+    <t>60 A</t>
+  </si>
+  <si>
+    <t>30 A</t>
+  </si>
+  <si>
+    <t>Caixa dos fusíveis</t>
+  </si>
+  <si>
+    <t>Led</t>
+  </si>
+  <si>
+    <t>Branco Pequeno</t>
+  </si>
+  <si>
+    <t>Branco Grande</t>
+  </si>
+  <si>
+    <t>Vermelho Pequeno</t>
+  </si>
+  <si>
+    <t>Vermelho Grande</t>
+  </si>
+  <si>
+    <t>Verde pequeno</t>
+  </si>
+  <si>
+    <t>Verde Grande</t>
+  </si>
+  <si>
+    <t>Azul pequeno</t>
+  </si>
+  <si>
+    <t>Azul Grande</t>
+  </si>
+  <si>
+    <t>Led Branco Pequeno</t>
+  </si>
+  <si>
+    <t>Led Branco Grande</t>
+  </si>
+  <si>
+    <t>Led Vermelho Pequeno</t>
+  </si>
+  <si>
+    <t>Led Vermelho Grande</t>
+  </si>
+  <si>
+    <t>Led Verde Grande</t>
+  </si>
+  <si>
+    <t>Led verde pequeno</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Led Azul pequeno </t>
+  </si>
+  <si>
+    <t>Led Azul grande</t>
+  </si>
+  <si>
+    <t>Caixa dos leds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -669,7 +1010,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -697,6 +1038,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -731,7 +1102,9 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -739,11 +1112,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -760,13 +1130,74 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1087,1729 +1518,3251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EAFFE1C-1227-4168-9582-491BF80477F1}">
-  <dimension ref="A1:G75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
     <col min="5" max="5" width="33.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="F4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>17</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>12</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>12</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>4</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>10</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>96</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>15</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>2</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="F16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>12</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>4</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>47</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>8</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>9</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>14</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>17</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>82</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="4">
-        <v>16</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="D25" s="3">
+        <v>16</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>4</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="F26" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>0</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>2</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="F28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>4</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="F29" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>110</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>19</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>98</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="F32" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>57</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="F33" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>36</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>107</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F36" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="4" t="s">
+      <c r="F36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="3" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>49</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="4" t="s">
+      <c r="F37" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="3" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>41</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="F38" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="3" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>50</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G39" s="4" t="s">
+      <c r="G39" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
+      <c r="A40" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>19</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E40" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="F40" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>22</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F41" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" s="4" t="s">
+      <c r="F41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="3" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>45</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="F42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="3" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="F43" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="3">
         <v>119</v>
       </c>
-      <c r="E44" s="8" t="s">
+      <c r="E44" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="8" t="s">
+      <c r="F44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="3">
         <v>50</v>
       </c>
-      <c r="E45" s="8" t="s">
+      <c r="E45" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F45" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="8" t="s">
+      <c r="F45" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="3">
         <v>15</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="8" t="s">
+      <c r="F46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="3">
         <v>52</v>
       </c>
-      <c r="E47" s="8" t="s">
+      <c r="E47" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F47" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G47" s="8" t="s">
+      <c r="F47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="3" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="3">
         <v>2</v>
       </c>
-      <c r="E48" s="8" t="s">
+      <c r="E48" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" s="8" t="s">
+      <c r="F48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="3">
         <v>6</v>
       </c>
-      <c r="E49" s="8" t="s">
+      <c r="E49" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F49" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G49" s="8" t="s">
+      <c r="F49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="3">
         <v>85</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="8" t="s">
+      <c r="F50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="3">
         <v>55</v>
       </c>
-      <c r="E51" s="8" t="s">
+      <c r="E51" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F51" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" s="8" t="s">
+      <c r="F51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="3">
         <v>119</v>
       </c>
-      <c r="E52" s="8" t="s">
+      <c r="E52" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G52" s="8" t="s">
+      <c r="F52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G52" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="3">
         <v>2</v>
       </c>
-      <c r="E53" s="8" t="s">
+      <c r="E53" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F53" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" s="8" t="s">
+      <c r="F53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="3">
         <v>2</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G54" s="8" t="s">
+      <c r="F54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="3">
         <v>58</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E55" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F55" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G55" s="8" t="s">
+      <c r="F55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="3" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="3">
         <v>1</v>
       </c>
-      <c r="E56" s="8" t="s">
+      <c r="E56" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G56" s="8" t="s">
+      <c r="F56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="3">
         <v>4</v>
       </c>
-      <c r="E57" s="8" t="s">
+      <c r="E57" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F57" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G57" s="8" t="s">
+      <c r="F57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="3">
         <v>1</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F58" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="8" t="s">
+      <c r="F58" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="3">
         <v>50</v>
       </c>
-      <c r="E59" s="8" t="s">
+      <c r="E59" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F59" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="8" t="s">
+      <c r="F59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="3">
         <v>55</v>
       </c>
-      <c r="E60" s="8" t="s">
+      <c r="E60" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G60" s="8" t="s">
+      <c r="F60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="3" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="3">
         <v>53</v>
       </c>
-      <c r="E61" s="8" t="s">
+      <c r="E61" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F61" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G61" s="8" t="s">
+      <c r="F61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="3" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="3">
         <v>19</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F62" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="8" t="s">
+      <c r="F62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="3">
         <v>4</v>
       </c>
-      <c r="E63" s="8" t="s">
+      <c r="E63" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F63" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G63" s="8" t="s">
+      <c r="F63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="3">
         <v>70</v>
       </c>
-      <c r="E64" s="8" t="s">
+      <c r="E64" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F64" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G64" s="8" t="s">
+      <c r="F64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="3">
         <v>14</v>
       </c>
-      <c r="E65" s="8" t="s">
+      <c r="E65" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F65" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G65" s="8" t="s">
+      <c r="F65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="3" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="3">
         <v>1</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F66" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G66" s="8" t="s">
+      <c r="F66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="3" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="3">
         <v>49</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E67" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="F67" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G67" s="8" t="s">
+      <c r="F67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G67" s="3" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="3">
         <v>1</v>
       </c>
-      <c r="E68" s="8" t="s">
+      <c r="E68" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" s="8" t="s">
+      <c r="F68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G68" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="3">
         <v>1</v>
       </c>
-      <c r="E69" s="8" t="s">
+      <c r="E69" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F69" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G69" s="8" t="s">
+      <c r="F69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G69" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="3">
         <v>1</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F70" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G70" s="8" t="s">
+      <c r="F70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G70" s="3" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="3">
         <v>1</v>
       </c>
-      <c r="E71" s="8" t="s">
+      <c r="E71" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F71" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G71" s="8" t="s">
+      <c r="F71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G71" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="3">
         <v>1</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="E72" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F72" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" s="8" t="s">
+      <c r="F72" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G72" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="3">
         <v>1</v>
       </c>
-      <c r="E73" s="8" t="s">
+      <c r="E73" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F73" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G73" s="8" t="s">
+      <c r="F73" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="3">
         <v>1</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G74" s="8" t="s">
+      <c r="F74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="3" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="3">
         <v>1</v>
       </c>
-      <c r="E75" s="8" t="s">
+      <c r="E75" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F75" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G75" s="8" t="s">
+      <c r="F75" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>206</v>
       </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D76" s="10">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" s="10">
+        <v>10</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="D78" s="10">
+        <v>5</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="D79" s="11">
+        <v>30</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="D80" s="11">
+        <v>30</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="D81" s="17">
+        <v>1</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="D82" s="10">
+        <v>2</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D83" s="10">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="D84" s="10">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="D85" s="10">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D86" s="10">
+        <v>2</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="D87" s="10">
+        <v>5</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="D88" s="10">
+        <v>3</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D89" s="10">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D90" s="10">
+        <v>1</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D91" s="10">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D92" s="10">
+        <v>6</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="D93" s="10">
+        <v>9</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="D94" s="10">
+        <v>10</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C95" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="D95" s="11">
+        <v>2</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D96" s="11">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C97" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="D97" s="22">
+        <v>1</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G97" s="18" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B98" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="D98" s="10">
+        <v>10</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="B99" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D99" s="10">
+        <v>10</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" s="10">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="20" t="s">
+        <v>248</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C101" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="D101" s="22">
+        <v>7</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G101" s="18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D102" s="10">
+        <v>2</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G102" s="1"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D103" s="10">
+        <v>9</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G103" s="1"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D104" s="10">
+        <v>11</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="C105" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="D105" s="22">
+        <v>4</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>255</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G105" s="27"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B106" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D106" s="10">
+        <v>34</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B107" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D107" s="10">
+        <v>2</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B108" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D108" s="10">
+        <v>1</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D109" s="10">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G109" s="1"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D110" s="10">
+        <v>1</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G110" s="1"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D111" s="10">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G111" s="1"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>266</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D112" s="10">
+        <v>22</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="B113" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C113" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="D113" s="22">
+        <v>3</v>
+      </c>
+      <c r="E113" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="27"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D114" s="10">
+        <v>3</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G114" s="1"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D115" s="10">
+        <v>9</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G115" s="1"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D116" s="10">
+        <v>7</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" s="1"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D117" s="10">
+        <v>4</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G117" s="1"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B118" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D118" s="10">
+        <v>3</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G118" s="1"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="B119" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D119" s="11">
+        <v>2</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="1"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D120" s="10">
+        <v>4</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G120" s="1"/>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B121" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D121" s="10">
+        <v>2</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G121" s="1"/>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="B122" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D122" s="10">
+        <v>3</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G122" s="1"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="B123" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D123" s="10">
+        <v>2</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="B124" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="C124" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="D124" s="17">
+        <v>24</v>
+      </c>
+      <c r="E124" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="27"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="D125" s="10">
+        <v>23</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G125" s="1"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="D126" s="10">
+        <v>4</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="1"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="D127" s="10">
+        <v>4</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="1"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B128" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D128" s="10">
+        <v>3</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B129" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D129" s="10">
+        <v>8</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D130" s="10">
+        <v>4</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G130" s="1"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B131" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="D131" s="10">
+        <v>2</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G131" s="1"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B132" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D132" s="10">
+        <v>1</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G132" s="1"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D133" s="10">
+        <v>25</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G133" s="1"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D134" s="10">
+        <v>2</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G134" s="1"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B135" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="D135" s="10">
+        <v>2</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G135" s="1"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="D136" s="10">
+        <v>1</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G136" s="1"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B137" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D137" s="17">
+        <v>1</v>
+      </c>
+      <c r="E137" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G137" s="27"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="B138" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D138" s="10">
+        <v>20</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G138" s="1"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="B139" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D139" s="10">
+        <v>20</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G139" s="1"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="B140" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D140" s="10">
+        <v>23</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G140" s="1"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="B141" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="D141" s="10">
+        <v>26</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="B142" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="D142" s="10">
+        <v>21</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G142" s="1"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B143" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="D143" s="10">
+        <v>20</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G143" s="1"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B144" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D144" s="10">
+        <v>20</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G144" s="1"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="B145" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D145" s="10">
+        <v>20</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G145" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\André Luis\OneDrive\Ambiente de Trabalho\Documentos\estoque_lab\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E73191-AC90-4686-8183-5D88761EF76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -24,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="321">
-  <si>
-    <t>Nome Equipamento</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="559">
   <si>
     <t>Tipo</t>
   </si>
@@ -101,9 +99,6 @@
     <t>Resistor de 4  Ω</t>
   </si>
   <si>
-    <t>8 Ω</t>
-  </si>
-  <si>
     <t>3,9  Ω</t>
   </si>
   <si>
@@ -515,18 +510,6 @@
     <t>1000 pF</t>
   </si>
   <si>
-    <t>2 nF</t>
-  </si>
-  <si>
-    <t>7 nF</t>
-  </si>
-  <si>
-    <t>8 nF</t>
-  </si>
-  <si>
-    <t>2 n F</t>
-  </si>
-  <si>
     <t>10 nF</t>
   </si>
   <si>
@@ -587,9 +570,6 @@
     <t>1500 uF</t>
   </si>
   <si>
-    <t>Diversos eletrolíticos</t>
-  </si>
-  <si>
     <t>Slot D2</t>
   </si>
   <si>
@@ -641,9 +621,6 @@
     <t>560 nF</t>
   </si>
   <si>
-    <t>Outros capacitores de cerâmica</t>
-  </si>
-  <si>
     <t>Slot D3 Diversos ceramica</t>
   </si>
   <si>
@@ -987,12 +964,750 @@
   </si>
   <si>
     <t>Caixa dos leds</t>
+  </si>
+  <si>
+    <t>Transistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suporte de LM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transistor 2n6133 </t>
+  </si>
+  <si>
+    <t>CI MC14012b</t>
+  </si>
+  <si>
+    <t>CI SN74LSO4N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI s4944 </t>
+  </si>
+  <si>
+    <t>31C</t>
+  </si>
+  <si>
+    <t>BD138</t>
+  </si>
+  <si>
+    <t>2n6133403</t>
+  </si>
+  <si>
+    <t>318BF244A</t>
+  </si>
+  <si>
+    <t>IRFF2807</t>
+  </si>
+  <si>
+    <t>em613c</t>
+  </si>
+  <si>
+    <t>7896ct</t>
+  </si>
+  <si>
+    <t>UTC945</t>
+  </si>
+  <si>
+    <t>2n6133</t>
+  </si>
+  <si>
+    <t>BU806</t>
+  </si>
+  <si>
+    <t>IRF 730</t>
+  </si>
+  <si>
+    <t>IRF 540</t>
+  </si>
+  <si>
+    <t>IRFBC2</t>
+  </si>
+  <si>
+    <t>Transitor BUL128d</t>
+  </si>
+  <si>
+    <t>Transistor 22380</t>
+  </si>
+  <si>
+    <t>Transistor 2n3886</t>
+  </si>
+  <si>
+    <t>Transistor d2499</t>
+  </si>
+  <si>
+    <t>Transistor BU808DF</t>
+  </si>
+  <si>
+    <t>DM7408n</t>
+  </si>
+  <si>
+    <t>NE555p</t>
+  </si>
+  <si>
+    <t>Opo7cp</t>
+  </si>
+  <si>
+    <t>LM741</t>
+  </si>
+  <si>
+    <t>LM308N</t>
+  </si>
+  <si>
+    <t>Suporte pino para LM</t>
+  </si>
+  <si>
+    <t>Nome Item</t>
+  </si>
+  <si>
+    <t>Caixa dos transistores e ci laranja</t>
+  </si>
+  <si>
+    <t>Diversos de CI</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Transistor BD138</t>
+  </si>
+  <si>
+    <t>Transistor 2n6133403</t>
+  </si>
+  <si>
+    <t>Transitor 318BF244A</t>
+  </si>
+  <si>
+    <t>Transitor em613c</t>
+  </si>
+  <si>
+    <t>Transitor DM7408n</t>
+  </si>
+  <si>
+    <t>Transitor NE555p</t>
+  </si>
+  <si>
+    <t>Transitor Opo7cp</t>
+  </si>
+  <si>
+    <t>Transitor IRFF2807</t>
+  </si>
+  <si>
+    <t>Transitor LM741</t>
+  </si>
+  <si>
+    <t>Transitor 7896ct</t>
+  </si>
+  <si>
+    <t>Transitor UTC945</t>
+  </si>
+  <si>
+    <t>Transitor 2n6133</t>
+  </si>
+  <si>
+    <t>Transitor BU806</t>
+  </si>
+  <si>
+    <t>Transitor IRF 730</t>
+  </si>
+  <si>
+    <t>Transitor IRF 540</t>
+  </si>
+  <si>
+    <t>Transitor IRFBC2</t>
+  </si>
+  <si>
+    <t>Transitor  22380</t>
+  </si>
+  <si>
+    <t>Transitor 2n3886</t>
+  </si>
+  <si>
+    <t>Transitor d2499</t>
+  </si>
+  <si>
+    <t>Transitor BU808DF</t>
+  </si>
+  <si>
+    <t>Diversos de transistores</t>
+  </si>
+  <si>
+    <t>Slot TRBUL128d</t>
+  </si>
+  <si>
+    <t>Junto com TRBU808 DF e TRD 2499 E NPN</t>
+  </si>
+  <si>
+    <t>C5305D</t>
+  </si>
+  <si>
+    <t>TIP31C</t>
+  </si>
+  <si>
+    <t>IRF3205</t>
+  </si>
+  <si>
+    <t>MJE13007</t>
+  </si>
+  <si>
+    <t>IRF530m</t>
+  </si>
+  <si>
+    <t>2N7000</t>
+  </si>
+  <si>
+    <t>B55327</t>
+  </si>
+  <si>
+    <t>BC548</t>
+  </si>
+  <si>
+    <t>B5547</t>
+  </si>
+  <si>
+    <t>Transitor C5305D</t>
+  </si>
+  <si>
+    <t>Transitor TIP31C</t>
+  </si>
+  <si>
+    <t>Transitor IRF3205</t>
+  </si>
+  <si>
+    <t>Transitor MJE13007</t>
+  </si>
+  <si>
+    <t>Transitor IRF530m</t>
+  </si>
+  <si>
+    <t>Transitor 2N7000</t>
+  </si>
+  <si>
+    <t>Transitor B55327</t>
+  </si>
+  <si>
+    <t>Transitor BC548</t>
+  </si>
+  <si>
+    <t>Transitor B5547</t>
+  </si>
+  <si>
+    <t>Caixa de transistores azul</t>
+  </si>
+  <si>
+    <t>Módulo</t>
+  </si>
+  <si>
+    <t>módulo -32900t20d</t>
+  </si>
+  <si>
+    <t>módulo stepdown lm25965dc</t>
+  </si>
+  <si>
+    <t>módulo stepup</t>
+  </si>
+  <si>
+    <t>módulo RTC</t>
+  </si>
+  <si>
+    <t>módulo estado sólido modelo g3-mb202p3</t>
+  </si>
+  <si>
+    <t>amplificador pam8403</t>
+  </si>
+  <si>
+    <t>potenciometro x9c1035 3-5V DC</t>
+  </si>
+  <si>
+    <t>módulo wa044 conversor para serial</t>
+  </si>
+  <si>
+    <t>e15-usb-t2 conversor para serial</t>
+  </si>
+  <si>
+    <t>módulo SD card</t>
+  </si>
+  <si>
+    <t>módulo usb-stc-1sp</t>
+  </si>
+  <si>
+    <t>módulo lora modelo SX12776</t>
+  </si>
+  <si>
+    <t>módulo leitor de RFID RDM6300</t>
+  </si>
+  <si>
+    <t>Caixa de módulo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sensor </t>
+  </si>
+  <si>
+    <t>Buzzer</t>
+  </si>
+  <si>
+    <t>Pieso elétrico (varios tipos)</t>
+  </si>
+  <si>
+    <t>Módulo DHT22</t>
+  </si>
+  <si>
+    <t>Sensor ultrassonico HCsr04</t>
+  </si>
+  <si>
+    <t>DHt22</t>
+  </si>
+  <si>
+    <t>Módulo Sensor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caixa de sensores </t>
+  </si>
+  <si>
+    <t>Microcontrolador</t>
+  </si>
+  <si>
+    <t>lora 32 micro</t>
+  </si>
+  <si>
+    <t>esp32 cam</t>
+  </si>
+  <si>
+    <t>pic kit 3 conversor</t>
+  </si>
+  <si>
+    <t>STM Blackpil modelo 32f411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESP 32 dev kit 1 </t>
+  </si>
+  <si>
+    <t>ESP 32 dev kit 4</t>
+  </si>
+  <si>
+    <t>ESP 32 display</t>
+  </si>
+  <si>
+    <t>ESP 32 wifi</t>
+  </si>
+  <si>
+    <t>Esp 32 Display</t>
+  </si>
+  <si>
+    <t>Raspberry pi pico rp2040</t>
+  </si>
+  <si>
+    <t>adaptador de esp 32</t>
+  </si>
+  <si>
+    <t>pic 16f628A</t>
+  </si>
+  <si>
+    <t>ATtiny 85</t>
+  </si>
+  <si>
+    <t>módulo programador Attiny 85</t>
+  </si>
+  <si>
+    <t>RP2040 zero raspberry pi pico USB-C</t>
+  </si>
+  <si>
+    <t>Módulo Lora</t>
+  </si>
+  <si>
+    <t>Esp32</t>
+  </si>
+  <si>
+    <t>Pic</t>
+  </si>
+  <si>
+    <t>Raspberry</t>
+  </si>
+  <si>
+    <t>Adaptador</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATtiny </t>
+  </si>
+  <si>
+    <t>Caixa de microcontroladores</t>
+  </si>
+  <si>
+    <t>Kit resfriamento rasp CASE</t>
+  </si>
+  <si>
+    <t>Arduino UNO</t>
+  </si>
+  <si>
+    <t>Arduino com display</t>
+  </si>
+  <si>
+    <t>Display LCD arduino keypad shield</t>
+  </si>
+  <si>
+    <t>Arduino Mega</t>
+  </si>
+  <si>
+    <t>Conversor programador PIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raspberry pi 4 model 3 </t>
+  </si>
+  <si>
+    <t>cabo flat de extensão para raspberry</t>
+  </si>
+  <si>
+    <t>Caixa microcontrolador raspberry e arduino</t>
+  </si>
+  <si>
+    <t>Kit resfriamento Case</t>
+  </si>
+  <si>
+    <t>Arduino</t>
+  </si>
+  <si>
+    <t>Caixa de adaptadores e impressora</t>
+  </si>
+  <si>
+    <t>Pen Drive</t>
+  </si>
+  <si>
+    <t>MicroSD</t>
+  </si>
+  <si>
+    <t>Adaptador micro SD para slot TF</t>
+  </si>
+  <si>
+    <t>Adaptador USP para tipo C</t>
+  </si>
+  <si>
+    <t>Refil para impressora da etiquetadora</t>
+  </si>
+  <si>
+    <t>Refil para impressora</t>
+  </si>
+  <si>
+    <t>Diodo</t>
+  </si>
+  <si>
+    <t>Znin4728</t>
+  </si>
+  <si>
+    <t>in4148</t>
+  </si>
+  <si>
+    <t>in4007</t>
+  </si>
+  <si>
+    <t>in 4937</t>
+  </si>
+  <si>
+    <t>p6ke200</t>
+  </si>
+  <si>
+    <t>sa5420</t>
+  </si>
+  <si>
+    <t>fr103</t>
+  </si>
+  <si>
+    <t>zener sem modelo</t>
+  </si>
+  <si>
+    <t>sk3402</t>
+  </si>
+  <si>
+    <t>iv5ke400a</t>
+  </si>
+  <si>
+    <t>in5406</t>
+  </si>
+  <si>
+    <t>5a15ca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sas0a </t>
+  </si>
+  <si>
+    <t>fr102</t>
+  </si>
+  <si>
+    <t>in4001</t>
+  </si>
+  <si>
+    <t>in5819</t>
+  </si>
+  <si>
+    <t>mbr1545ct</t>
+  </si>
+  <si>
+    <t>h326</t>
+  </si>
+  <si>
+    <t>pwm0122</t>
+  </si>
+  <si>
+    <t>mospecf10c20</t>
+  </si>
+  <si>
+    <t>1l0380r</t>
+  </si>
+  <si>
+    <t>sb2040</t>
+  </si>
+  <si>
+    <t>6v2z2</t>
+  </si>
+  <si>
+    <t>fr107</t>
+  </si>
+  <si>
+    <t>fr104</t>
+  </si>
+  <si>
+    <t>Caixa de diodos</t>
+  </si>
+  <si>
+    <t>4 Ω</t>
+  </si>
+  <si>
+    <t>2,2 nF</t>
+  </si>
+  <si>
+    <t>4,7 nF</t>
+  </si>
+  <si>
+    <t>6,8 nF</t>
+  </si>
+  <si>
+    <t>8,2 nF</t>
+  </si>
+  <si>
+    <t>CI LM358p</t>
+  </si>
+  <si>
+    <t>LM358p</t>
+  </si>
+  <si>
+    <t>CI 31C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI CI s4944 </t>
+  </si>
+  <si>
+    <t>CI CI SN74LSO4N</t>
+  </si>
+  <si>
+    <t>CI CI MC14012b</t>
+  </si>
+  <si>
+    <t>Slot 358P</t>
+  </si>
+  <si>
+    <t>CI LM3930</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slot </t>
+  </si>
+  <si>
+    <t>CI LM308N</t>
+  </si>
+  <si>
+    <t>Transistor STR w5753a</t>
+  </si>
+  <si>
+    <t>STR w5753a</t>
+  </si>
+  <si>
+    <t>Slot STR w5753a</t>
+  </si>
+  <si>
+    <t>Transistor STR g8656</t>
+  </si>
+  <si>
+    <t>STR 68656</t>
+  </si>
+  <si>
+    <t>Slot STR 68656</t>
+  </si>
+  <si>
+    <t>Slot C5305D</t>
+  </si>
+  <si>
+    <t>Slot TIP31C</t>
+  </si>
+  <si>
+    <t>Slot IRF530m</t>
+  </si>
+  <si>
+    <t>Slot IRF3205</t>
+  </si>
+  <si>
+    <t>Slot MJE13007</t>
+  </si>
+  <si>
+    <t>Slot 2N7000</t>
+  </si>
+  <si>
+    <t>Slot B55327</t>
+  </si>
+  <si>
+    <t>Slot BC548</t>
+  </si>
+  <si>
+    <t>Slot B5547</t>
+  </si>
+  <si>
+    <t>Acessórios</t>
+  </si>
+  <si>
+    <t>módulo lora 32 micro</t>
+  </si>
+  <si>
+    <t>Slot 32900</t>
+  </si>
+  <si>
+    <t>Slot stepup</t>
+  </si>
+  <si>
+    <t>Slot módulo</t>
+  </si>
+  <si>
+    <t>Slot stepdown</t>
+  </si>
+  <si>
+    <t>Slot estado sólido</t>
+  </si>
+  <si>
+    <t>Slot amplificador 8403</t>
+  </si>
+  <si>
+    <t>Slot potenciometro x9</t>
+  </si>
+  <si>
+    <t>Slot conversor</t>
+  </si>
+  <si>
+    <t>Slot SD card</t>
+  </si>
+  <si>
+    <t>Slot lora</t>
+  </si>
+  <si>
+    <t>Slot RFID</t>
+  </si>
+  <si>
+    <t>Slot Buzzer</t>
+  </si>
+  <si>
+    <t>Slot Pieso</t>
+  </si>
+  <si>
+    <t>Slot pic</t>
+  </si>
+  <si>
+    <t>Slot STM</t>
+  </si>
+  <si>
+    <t>Slot ESP</t>
+  </si>
+  <si>
+    <t>Slot resfriamento</t>
+  </si>
+  <si>
+    <t>Slot Arduino</t>
+  </si>
+  <si>
+    <t>Slot DHT</t>
+  </si>
+  <si>
+    <t>Slot ultrassonico</t>
+  </si>
+  <si>
+    <t>Slot cam</t>
+  </si>
+  <si>
+    <t>Slot kit</t>
+  </si>
+  <si>
+    <t>Slot display</t>
+  </si>
+  <si>
+    <t>Slot wifi</t>
+  </si>
+  <si>
+    <t>Slot Display</t>
+  </si>
+  <si>
+    <t>Slot pi</t>
+  </si>
+  <si>
+    <t>Slot programador</t>
+  </si>
+  <si>
+    <t>Slot Conversor</t>
+  </si>
+  <si>
+    <t>Slot raspberry</t>
+  </si>
+  <si>
+    <t>Slot cabo</t>
+  </si>
+  <si>
+    <t>Slot Pen</t>
+  </si>
+  <si>
+    <t>Slot Adaptador</t>
+  </si>
+  <si>
+    <t>Slot Refil</t>
+  </si>
+  <si>
+    <t>Slot 6v</t>
+  </si>
+  <si>
+    <t>Slot lora micro</t>
+  </si>
+  <si>
+    <t>Slot fr107</t>
+  </si>
+  <si>
+    <t>Slot Znin4728</t>
+  </si>
+  <si>
+    <t>Slot MicroSD</t>
+  </si>
+  <si>
+    <t>Slot raspbery rp2040</t>
+  </si>
+  <si>
+    <t>Slot Attiny 85</t>
+  </si>
+  <si>
+    <t>Slot de adaptador de ESP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zener </t>
+  </si>
+  <si>
+    <t>Antena Lora</t>
+  </si>
+  <si>
+    <t>Módulo antena lora</t>
+  </si>
+  <si>
+    <t>Caixa Antena lora</t>
+  </si>
+  <si>
+    <t>Slot da antena</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1010,7 +1725,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1071,8 +1786,122 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE99759"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9900FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93625"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF7C80"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80DE99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9933"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1108,11 +1937,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1200,6 +2053,135 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1208,7 +2190,13 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF9933"/>
+      <color rgb="FF80DE99"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFD93625"/>
       <color rgb="FF0099CC"/>
+      <color rgb="FF9900FF"/>
+      <color rgb="FFE99759"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1518,15 +2506,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G145"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="40.28515625" customWidth="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
-    <col min="3" max="3" width="36.28515625" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="33.85546875" customWidth="1"/>
+    <col min="5" max="5" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
     <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1542,3229 +2530,5780 @@
     </row>
     <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="F2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
+      <c r="E3" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
+      <c r="E4" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>10</v>
+      <c r="E5" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>10</v>
+      <c r="E6" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3">
         <v>17</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>10</v>
+      <c r="E7" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="D8" s="3">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>10</v>
+      <c r="E8" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3">
         <v>12</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>10</v>
+      <c r="E9" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>481</v>
       </c>
       <c r="D10" s="3">
         <v>8</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
+      <c r="E10" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="3">
         <v>4</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
+      <c r="E11" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D12" s="3">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
+      <c r="E12" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" s="3">
         <v>10</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>10</v>
+      <c r="E13" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="3">
         <v>96</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>10</v>
+      <c r="E14" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D15" s="3">
         <v>15</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>10</v>
+      <c r="E15" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D16" s="3">
         <v>2</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>10</v>
+      <c r="E16" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D17" s="3">
         <v>12</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>10</v>
+      <c r="E17" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D18" s="3">
         <v>4</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>10</v>
+      <c r="E18" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D19" s="3">
         <v>47</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>10</v>
+      <c r="E19" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3">
         <v>8</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>10</v>
+      <c r="E20" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D21" s="3">
         <v>9</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>10</v>
+      <c r="E21" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3">
         <v>14</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>10</v>
+      <c r="E22" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D23" s="3">
         <v>17</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>10</v>
+      <c r="E23" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D24" s="3">
         <v>82</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>10</v>
+      <c r="E24" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D25" s="3">
         <v>16</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>10</v>
+      <c r="E25" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D26" s="3">
         <v>4</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>10</v>
+      <c r="E26" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="3">
         <v>0</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>10</v>
+      <c r="E27" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D28" s="3">
         <v>2</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>10</v>
+      <c r="E28" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" s="3">
         <v>4</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>10</v>
+      <c r="E29" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D30" s="3">
         <v>110</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>10</v>
+      <c r="E30" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D31" s="3">
         <v>19</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>10</v>
+      <c r="E31" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D32" s="3">
         <v>98</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>10</v>
+      <c r="E32" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D33" s="3">
         <v>57</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>10</v>
+      <c r="E33" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" s="3">
         <v>36</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>10</v>
+      <c r="E34" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="D35" s="3">
         <v>107</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>10</v>
+      <c r="E35" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D36" s="3">
         <v>2</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>10</v>
+      <c r="E36" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D37" s="3">
         <v>49</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>10</v>
+      <c r="E37" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D38" s="3">
         <v>41</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>10</v>
+      <c r="E38" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D39" s="3">
         <v>50</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>10</v>
+      <c r="E39" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D40" s="3">
         <v>19</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>10</v>
+      <c r="E40" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D41" s="3">
         <v>22</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>10</v>
+      <c r="E41" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D42" s="3">
         <v>45</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>10</v>
+      <c r="E42" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>10</v>
+      <c r="E43" s="9" t="s">
+        <v>9</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D44" s="3">
         <v>119</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>182</v>
+      <c r="E44" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D45" s="3">
         <v>50</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>182</v>
+      <c r="E45" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D46" s="3">
         <v>15</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>182</v>
+      <c r="E46" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D47" s="3">
         <v>52</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>182</v>
+      <c r="E47" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D48" s="3">
         <v>2</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>182</v>
+      <c r="E48" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D49" s="3">
         <v>6</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>182</v>
+      <c r="E49" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D50" s="3">
         <v>85</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>182</v>
+      <c r="E50" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>163</v>
+        <v>482</v>
       </c>
       <c r="D51" s="3">
         <v>55</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>182</v>
+      <c r="E51" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>164</v>
+        <v>483</v>
       </c>
       <c r="D52" s="3">
         <v>119</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>182</v>
+      <c r="E52" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>165</v>
+        <v>484</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>182</v>
+      <c r="E53" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>166</v>
+        <v>485</v>
       </c>
       <c r="D54" s="3">
         <v>2</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>182</v>
+      <c r="E54" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="D55" s="3">
         <v>58</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>182</v>
+      <c r="E55" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>182</v>
+      <c r="E56" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D57" s="3">
         <v>4</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>182</v>
+      <c r="E57" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>182</v>
+      <c r="E58" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D59" s="3">
         <v>50</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>182</v>
+      <c r="E59" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D60" s="3">
         <v>55</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>182</v>
+      <c r="E60" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D61" s="3">
         <v>53</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>182</v>
+      <c r="E61" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D62" s="3">
         <v>19</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>182</v>
+      <c r="E62" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D63" s="3">
         <v>4</v>
       </c>
-      <c r="E63" s="3" t="s">
-        <v>182</v>
+      <c r="E63" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D64" s="3">
         <v>70</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>182</v>
+      <c r="E64" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D65" s="3">
         <v>14</v>
       </c>
-      <c r="E65" s="3" t="s">
-        <v>182</v>
+      <c r="E65" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>182</v>
+      <c r="E66" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D67" s="3">
         <v>49</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>182</v>
+      <c r="E67" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>187</v>
+      <c r="E68" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>187</v>
+      <c r="E69" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B70" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>205</v>
+      <c r="E70" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>205</v>
+      <c r="E71" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>205</v>
+      <c r="E72" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>205</v>
+      <c r="E73" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>205</v>
+      <c r="E74" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>205</v>
+      <c r="E75" s="60" t="s">
+        <v>176</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D76" s="10">
         <v>3</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>216</v>
+      <c r="E76" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D77" s="10">
         <v>10</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>216</v>
+      <c r="E77" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D78" s="10">
         <v>5</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>216</v>
+      <c r="E78" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D79" s="11">
         <v>30</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>216</v>
+      <c r="E79" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D80" s="11">
         <v>30</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>216</v>
+      <c r="E80" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="B81" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C81" s="14" t="s">
         <v>207</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="D81" s="17">
         <v>1</v>
       </c>
-      <c r="E81" s="18" t="s">
-        <v>216</v>
+      <c r="E81" s="61" t="s">
+        <v>208</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G81" s="18" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D82" s="10">
         <v>2</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>218</v>
+      <c r="E82" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D83" s="10">
         <v>5</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>218</v>
+      <c r="E83" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B84" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D84" s="10">
         <v>1</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>218</v>
+      <c r="E84" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="B85" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D85" s="10">
         <v>1</v>
       </c>
-      <c r="E85" s="3" t="s">
-        <v>218</v>
+      <c r="E85" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B86" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D86" s="10">
         <v>2</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>218</v>
+      <c r="E86" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B87" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D87" s="10">
         <v>5</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>218</v>
+      <c r="E87" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B88" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="D88" s="10">
         <v>3</v>
       </c>
-      <c r="E88" s="3" t="s">
-        <v>218</v>
+      <c r="E88" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B89" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D89" s="10">
         <v>1</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>218</v>
+      <c r="E89" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B90" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D90" s="10">
         <v>1</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>218</v>
+      <c r="E90" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B91" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="D91" s="10">
         <v>1</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>218</v>
+      <c r="E91" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B92" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D92" s="10">
         <v>6</v>
       </c>
-      <c r="E92" s="3" t="s">
-        <v>218</v>
+      <c r="E92" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B93" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="D93" s="10">
         <v>9</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>218</v>
+      <c r="E93" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B94" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="D94" s="10">
         <v>10</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>218</v>
+      <c r="E94" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B95" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D95" s="11">
         <v>2</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>218</v>
+      <c r="E95" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="16" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B96" s="19" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="D96" s="11">
         <v>5</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>218</v>
+      <c r="E96" s="62" t="s">
+        <v>210</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="20" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="C97" s="20" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D97" s="22">
         <v>1</v>
       </c>
-      <c r="E97" s="18" t="s">
-        <v>218</v>
+      <c r="E97" s="63" t="s">
+        <v>210</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G97" s="18" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="D98" s="10">
         <v>10</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>240</v>
+      <c r="E98" s="64" t="s">
+        <v>232</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D99" s="10">
         <v>10</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>240</v>
+      <c r="E99" s="64" t="s">
+        <v>232</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="16" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="B100" s="23" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D100" s="10">
         <v>5</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>240</v>
+      <c r="E100" s="64" t="s">
+        <v>232</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="20" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B101" s="24" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C101" s="22" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D101" s="22">
         <v>7</v>
       </c>
-      <c r="E101" s="18" t="s">
-        <v>240</v>
+      <c r="E101" s="65" t="s">
+        <v>232</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G101" s="18" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B102" s="25" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D102" s="10">
         <v>2</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>255</v>
+      <c r="E102" s="66" t="s">
+        <v>247</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G102" s="1"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B103" s="25" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D103" s="10">
         <v>9</v>
       </c>
-      <c r="E103" s="3" t="s">
-        <v>255</v>
+      <c r="E103" s="66" t="s">
+        <v>247</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="16" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B104" s="25" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D104" s="10">
         <v>11</v>
       </c>
-      <c r="E104" s="3" t="s">
-        <v>255</v>
+      <c r="E104" s="66" t="s">
+        <v>247</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G104" s="1"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="20" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B105" s="26" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C105" s="22" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="D105" s="22">
         <v>4</v>
       </c>
-      <c r="E105" s="18" t="s">
-        <v>255</v>
+      <c r="E105" s="67" t="s">
+        <v>247</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G105" s="27"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B106" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D106" s="10">
         <v>34</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>257</v>
+      <c r="E106" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G106" s="1"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B107" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D107" s="10">
         <v>2</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>257</v>
+      <c r="E107" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G107" s="1"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B108" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D108" s="10">
         <v>1</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>257</v>
+      <c r="E108" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G108" s="1"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B109" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D109" s="10">
         <v>1</v>
       </c>
-      <c r="E109" s="3" t="s">
-        <v>257</v>
+      <c r="E109" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G109" s="1"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B110" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D110" s="10">
         <v>1</v>
       </c>
-      <c r="E110" s="3" t="s">
-        <v>257</v>
+      <c r="E110" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G110" s="1"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="D111" s="10">
         <v>1</v>
       </c>
-      <c r="E111" s="3" t="s">
-        <v>257</v>
+      <c r="E111" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="16" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B112" s="28" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="D112" s="10">
         <v>22</v>
       </c>
-      <c r="E112" s="3" t="s">
-        <v>257</v>
+      <c r="E112" s="68" t="s">
+        <v>249</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G112" s="1"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B113" s="29" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C113" s="18" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D113" s="22">
         <v>3</v>
       </c>
-      <c r="E113" s="18" t="s">
-        <v>257</v>
+      <c r="E113" s="69" t="s">
+        <v>249</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G113" s="27"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D114" s="10">
         <v>3</v>
       </c>
-      <c r="E114" s="3" t="s">
-        <v>268</v>
+      <c r="E114" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G114" s="1"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D115" s="10">
         <v>9</v>
       </c>
-      <c r="E115" s="3" t="s">
-        <v>268</v>
+      <c r="E115" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G115" s="1"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B116" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D116" s="10">
         <v>7</v>
       </c>
-      <c r="E116" s="3" t="s">
-        <v>268</v>
+      <c r="E116" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G116" s="1"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B117" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="D117" s="10">
         <v>4</v>
       </c>
-      <c r="E117" s="3" t="s">
-        <v>268</v>
+      <c r="E117" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G117" s="1"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B118" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D118" s="10">
         <v>3</v>
       </c>
-      <c r="E118" s="3" t="s">
-        <v>268</v>
+      <c r="E118" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G118" s="1"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B119" s="16" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="D119" s="11">
         <v>2</v>
       </c>
-      <c r="E119" s="3" t="s">
-        <v>268</v>
+      <c r="E119" s="70" t="s">
+        <v>260</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="B120" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
+      </c>
+      <c r="B120" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D120" s="10">
         <v>4</v>
       </c>
-      <c r="E120" s="3" t="s">
-        <v>281</v>
+      <c r="E120" s="37" t="s">
+        <v>273</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="B121" s="16" t="s">
         <v>275</v>
       </c>
+      <c r="B121" s="23" t="s">
+        <v>267</v>
+      </c>
       <c r="C121" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="D121" s="10">
         <v>2</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>281</v>
+      <c r="E121" s="37" t="s">
+        <v>273</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="B122" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D122" s="10">
         <v>3</v>
       </c>
-      <c r="E122" s="3" t="s">
-        <v>281</v>
+      <c r="E122" s="37" t="s">
+        <v>273</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="B123" s="16" t="s">
-        <v>275</v>
+        <v>277</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D123" s="10">
         <v>2</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>281</v>
+      <c r="E123" s="37" t="s">
+        <v>273</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="B124" s="20" t="s">
-        <v>275</v>
+        <v>278</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>267</v>
       </c>
       <c r="C124" s="30" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="D124" s="17">
         <v>24</v>
       </c>
-      <c r="E124" s="18" t="s">
-        <v>281</v>
+      <c r="E124" s="55" t="s">
+        <v>273</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G124" s="27"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B125" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="D125" s="10">
         <v>23</v>
       </c>
-      <c r="E125" s="3" t="s">
-        <v>302</v>
+      <c r="E125" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B126" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D126" s="10">
         <v>4</v>
       </c>
-      <c r="E126" s="3" t="s">
-        <v>302</v>
+      <c r="E126" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B127" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="D127" s="10">
         <v>4</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>302</v>
+      <c r="E127" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B128" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D128" s="10">
         <v>3</v>
       </c>
-      <c r="E128" s="3" t="s">
-        <v>302</v>
+      <c r="E128" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D129" s="10">
         <v>8</v>
       </c>
-      <c r="E129" s="3" t="s">
-        <v>302</v>
+      <c r="E129" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B130" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B130" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="D130" s="10">
         <v>4</v>
       </c>
-      <c r="E130" s="3" t="s">
-        <v>302</v>
+      <c r="E130" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B131" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>287</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>295</v>
       </c>
       <c r="D131" s="10">
         <v>2</v>
       </c>
-      <c r="E131" s="3" t="s">
-        <v>302</v>
+      <c r="E131" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B132" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>288</v>
-      </c>
-      <c r="B132" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>296</v>
       </c>
       <c r="D132" s="10">
         <v>1</v>
       </c>
-      <c r="E132" s="3" t="s">
-        <v>302</v>
+      <c r="E132" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B133" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B133" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D133" s="10">
         <v>25</v>
       </c>
-      <c r="E133" s="3" t="s">
-        <v>302</v>
+      <c r="E133" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B134" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D134" s="10">
         <v>2</v>
       </c>
-      <c r="E134" s="3" t="s">
-        <v>302</v>
+      <c r="E134" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G134" s="1"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B135" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B135" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="D135" s="10">
         <v>2</v>
       </c>
-      <c r="E135" s="3" t="s">
-        <v>302</v>
+      <c r="E135" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="B136" s="16" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B136" s="31" t="s">
+        <v>279</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D136" s="10">
         <v>1</v>
       </c>
-      <c r="E136" s="3" t="s">
-        <v>302</v>
+      <c r="E136" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G136" s="1"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="B137" s="20" t="s">
-        <v>287</v>
+        <v>280</v>
+      </c>
+      <c r="B137" s="32" t="s">
+        <v>279</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D137" s="17">
         <v>1</v>
       </c>
-      <c r="E137" s="18" t="s">
-        <v>302</v>
+      <c r="E137" s="72" t="s">
+        <v>294</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G137" s="27"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="B138" s="16" t="s">
-        <v>303</v>
+        <v>304</v>
+      </c>
+      <c r="B138" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D138" s="10">
         <v>20</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G138" s="1"/>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>303</v>
+        <v>305</v>
+      </c>
+      <c r="B139" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="D139" s="10">
         <v>20</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G139" s="1"/>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="B140" s="16" t="s">
-        <v>303</v>
+        <v>306</v>
+      </c>
+      <c r="B140" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D140" s="10">
         <v>23</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G140" s="1"/>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="B141" s="16" t="s">
-        <v>303</v>
+        <v>307</v>
+      </c>
+      <c r="B141" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D141" s="10">
         <v>26</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G141" s="1"/>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="16" t="s">
-        <v>317</v>
-      </c>
-      <c r="B142" s="16" t="s">
-        <v>303</v>
+        <v>309</v>
+      </c>
+      <c r="B142" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D142" s="10">
         <v>21</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G142" s="1"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="B143" s="16" t="s">
-        <v>303</v>
+        <v>308</v>
+      </c>
+      <c r="B143" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D143" s="10">
         <v>20</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G143" s="1"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B144" s="16" t="s">
-        <v>303</v>
+        <v>310</v>
+      </c>
+      <c r="B144" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D144" s="10">
         <v>20</v>
       </c>
       <c r="E144" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="1"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D145" s="17">
+        <v>20</v>
+      </c>
+      <c r="E145" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="27"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B146" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C146" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="D146" s="36">
+        <v>12</v>
+      </c>
+      <c r="E146" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" s="2"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B147" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D147" s="36">
+        <v>2</v>
+      </c>
+      <c r="E147" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="B148" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C148" s="36" t="s">
+        <v>316</v>
+      </c>
+      <c r="D148" s="36">
+        <v>1</v>
+      </c>
+      <c r="E148" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="B149" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C149" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D149" s="36">
+        <v>1</v>
+      </c>
+      <c r="E149" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="B150" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C150" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="D150" s="36">
+        <v>1</v>
+      </c>
+      <c r="E150" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B151" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="D151" s="10">
+        <v>2</v>
+      </c>
+      <c r="E151" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C152" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="F144" s="5" t="s">
+      <c r="D152" s="10">
+        <v>1</v>
+      </c>
+      <c r="E152" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="B153" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D153" s="10">
+        <v>1</v>
+      </c>
+      <c r="E153" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C154" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="D154" s="10">
+        <v>1</v>
+      </c>
+      <c r="E154" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="B155" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="D155" s="10">
+        <v>4</v>
+      </c>
+      <c r="E155" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F155" s="5"/>
+      <c r="G155" s="2" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="B156" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C156" s="10" t="s">
+        <v>497</v>
+      </c>
+      <c r="D156" s="10">
+        <v>4</v>
+      </c>
+      <c r="E156" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B157" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D157" s="10">
+        <v>1</v>
+      </c>
+      <c r="E157" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D158" s="10">
+        <v>1</v>
+      </c>
+      <c r="E158" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B159" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C159" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="D159" s="10">
+        <v>1</v>
+      </c>
+      <c r="E159" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B160" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C160" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D160" s="10">
+        <v>1</v>
+      </c>
+      <c r="E160" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B161" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D161" s="10">
+        <v>1</v>
+      </c>
+      <c r="E161" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="D162" s="10">
+        <v>1</v>
+      </c>
+      <c r="E162" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C163" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="D163" s="10">
+        <v>1</v>
+      </c>
+      <c r="E163" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D164" s="10">
+        <v>1</v>
+      </c>
+      <c r="E164" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="D165" s="10">
+        <v>1</v>
+      </c>
+      <c r="E165" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B166" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="D166" s="10">
+        <v>5</v>
+      </c>
+      <c r="E166" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B167" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C167" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="D167" s="10">
+        <v>1</v>
+      </c>
+      <c r="E167" s="38" t="s">
+        <v>344</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="57" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B168" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="D168" s="10">
+        <v>2</v>
+      </c>
+      <c r="E168" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="58"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B169" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D169" s="10">
+        <v>3</v>
+      </c>
+      <c r="E169" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G169" s="58"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B170" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D170" s="10">
+        <v>1</v>
+      </c>
+      <c r="E170" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G170" s="59"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B171" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="D171" s="10">
+        <v>1</v>
+      </c>
+      <c r="E171" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="B172" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>493</v>
+      </c>
+      <c r="D172" s="10">
+        <v>27</v>
+      </c>
+      <c r="E172" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="B173" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="D173" s="10">
+        <v>1</v>
+      </c>
+      <c r="E173" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="B174" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="D174" s="10">
+        <v>2</v>
+      </c>
+      <c r="E174" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="2"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B175" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="D175" s="10">
+        <v>1</v>
+      </c>
+      <c r="E175" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" s="2"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="B176" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="D176" s="10">
+        <v>1</v>
+      </c>
+      <c r="E176" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="2"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="B177" s="35" t="s">
+        <v>346</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="D177" s="10">
+        <v>1</v>
+      </c>
+      <c r="E177" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="B178" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C178" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D178" s="10">
+        <v>5</v>
+      </c>
+      <c r="E178" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="B179" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D179" s="10">
+        <v>2</v>
+      </c>
+      <c r="E179" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="B180" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="D180" s="10">
+        <v>10</v>
+      </c>
+      <c r="E180" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="B181" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="D181" s="10">
+        <v>9</v>
+      </c>
+      <c r="E181" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="B182" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D182" s="10">
+        <v>13</v>
+      </c>
+      <c r="E182" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="B183" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="D183" s="10">
+        <v>10</v>
+      </c>
+      <c r="E183" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="B184" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D184" s="10">
+        <v>5</v>
+      </c>
+      <c r="E184" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="B185" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="D185" s="10">
+        <v>8</v>
+      </c>
+      <c r="E185" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B186" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C186" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D186" s="17">
+        <v>7</v>
+      </c>
+      <c r="E186" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B187" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D187" s="10">
+        <v>14</v>
+      </c>
+      <c r="E187" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="B188" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="D188" s="10">
+        <v>4</v>
+      </c>
+      <c r="E188" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B189" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C189" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="D189" s="10">
+        <v>4</v>
+      </c>
+      <c r="E189" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B190" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C190" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D190" s="10">
+        <v>10</v>
+      </c>
+      <c r="E190" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B191" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C191" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D191" s="10">
+        <v>3</v>
+      </c>
+      <c r="E191" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="B192" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C192" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D192" s="10">
+        <v>1</v>
+      </c>
+      <c r="E192" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B193" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="D193" s="10">
+        <v>2</v>
+      </c>
+      <c r="E193" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="B194" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C194" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="D194" s="10">
+        <v>3</v>
+      </c>
+      <c r="E194" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B195" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="D195" s="10">
+        <v>2</v>
+      </c>
+      <c r="E195" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="B196" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C196" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="D196" s="10">
+        <v>10</v>
+      </c>
+      <c r="E196" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B197" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="D197" s="10">
+        <v>3</v>
+      </c>
+      <c r="E197" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="B198" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="D198" s="10">
+        <v>4</v>
+      </c>
+      <c r="E198" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D199" s="10">
+        <v>1</v>
+      </c>
+      <c r="E199" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="B200" s="73" t="s">
+        <v>556</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="D200" s="10">
+        <v>14</v>
+      </c>
+      <c r="E200" s="42" t="s">
+        <v>557</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B201" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D201" s="10">
+        <v>2</v>
+      </c>
+      <c r="E201" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B202" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C202" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D202" s="10">
+        <v>4</v>
+      </c>
+      <c r="E202" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B203" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C203" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D203" s="10">
+        <v>1</v>
+      </c>
+      <c r="E203" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B204" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C204" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D204" s="11">
+        <v>1</v>
+      </c>
+      <c r="E204" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B205" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D205" s="11">
+        <v>1</v>
+      </c>
+      <c r="E205" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G205" s="1"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="B206" s="50" t="s">
+        <v>428</v>
+      </c>
+      <c r="C206" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="D206" s="10">
+        <v>4</v>
+      </c>
+      <c r="E206" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B207" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D207" s="10">
+        <v>1</v>
+      </c>
+      <c r="E207" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B208" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C208" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="D208" s="11">
+        <v>2</v>
+      </c>
+      <c r="E208" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B209" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D209" s="11">
+        <v>10</v>
+      </c>
+      <c r="E209" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B210" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C210" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D210" s="10">
+        <v>9</v>
+      </c>
+      <c r="E210" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B211" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C211" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D211" s="10">
+        <v>6</v>
+      </c>
+      <c r="E211" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B212" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C212" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D212" s="10">
+        <v>1</v>
+      </c>
+      <c r="E212" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B213" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C213" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D213" s="11">
+        <v>1</v>
+      </c>
+      <c r="E213" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B214" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="D214" s="11">
+        <v>1</v>
+      </c>
+      <c r="E214" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B215" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D215" s="10">
+        <v>5</v>
+      </c>
+      <c r="E215" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B216" s="45" t="s">
+        <v>429</v>
+      </c>
+      <c r="C216" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="D216" s="10">
+        <v>3</v>
+      </c>
+      <c r="E216" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B217" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="D217" s="10">
+        <v>3</v>
+      </c>
+      <c r="E217" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B218" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="C218" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="D218" s="11">
+        <v>2</v>
+      </c>
+      <c r="E218" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B219" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="C219" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="D219" s="11">
+        <v>3</v>
+      </c>
+      <c r="E219" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B220" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="C220" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="D220" s="11">
+        <v>10</v>
+      </c>
+      <c r="E220" s="51" t="s">
+        <v>435</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="B221" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="C221" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D221" s="10">
+        <v>2</v>
+      </c>
+      <c r="E221" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>437</v>
+      </c>
+      <c r="D222" s="10">
+        <v>2</v>
+      </c>
+      <c r="E222" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F222" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D223" s="10">
+        <v>1</v>
+      </c>
+      <c r="E223" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F223" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C224" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="D224" s="11">
+        <v>1</v>
+      </c>
+      <c r="E224" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F224" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C225" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D225" s="11">
+        <v>1</v>
+      </c>
+      <c r="E225" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F225" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B226" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C226" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D226" s="10">
+        <v>2</v>
+      </c>
+      <c r="E226" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B227" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="C227" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D227" s="10">
+        <v>2</v>
+      </c>
+      <c r="E227" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="B228" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="C228" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="D228" s="17">
+        <v>3</v>
+      </c>
+      <c r="E228" s="54" t="s">
+        <v>444</v>
+      </c>
+      <c r="F228" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" s="27" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="B229" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="C229" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="D229" s="10">
+        <v>5</v>
+      </c>
+      <c r="E229" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="F229" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="B230" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C230" s="10" t="s">
+        <v>449</v>
+      </c>
+      <c r="D230" s="10">
+        <v>5</v>
+      </c>
+      <c r="E230" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="F230" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B231" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C231" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D231" s="10">
+        <v>1</v>
+      </c>
+      <c r="E231" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="F231" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B232" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D232" s="11">
+        <v>1</v>
+      </c>
+      <c r="E232" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="B233" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="C233" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="D233" s="22">
+        <v>1</v>
+      </c>
+      <c r="E233" s="55" t="s">
+        <v>447</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G233" s="27" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B234" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C234" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D234" s="10">
+        <v>100</v>
+      </c>
+      <c r="E234" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B235" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C235" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="D235" s="10">
+        <v>92</v>
+      </c>
+      <c r="E235" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F235" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G235" s="1"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C236" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="D236" s="10">
+        <v>69</v>
+      </c>
+      <c r="E236" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G236" s="1"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B237" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C237" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D237" s="10">
         <v>16</v>
       </c>
-      <c r="G144" s="1"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="16" t="s">
-        <v>319</v>
-      </c>
-      <c r="B145" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="C145" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="D145" s="10">
-        <v>20</v>
-      </c>
-      <c r="E145" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G145" s="1"/>
+      <c r="E237" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F237" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G237" s="1"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B238" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C238" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="D238" s="10">
+        <v>7</v>
+      </c>
+      <c r="E238" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G238" s="1"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B239" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C239" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="D239" s="10">
+        <v>3</v>
+      </c>
+      <c r="E239" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F239" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G239" s="1"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B240" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C240" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="D240" s="10">
+        <v>5</v>
+      </c>
+      <c r="E240" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B241" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C241" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="D241" s="10">
+        <v>3</v>
+      </c>
+      <c r="E241" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G241" s="1"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B242" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C242" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D242" s="10">
+        <v>1</v>
+      </c>
+      <c r="E242" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F242" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G242" s="1"/>
+    </row>
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A243" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B243" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C243" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="D243" s="10">
+        <v>2</v>
+      </c>
+      <c r="E243" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F243" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G243" s="1"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B244" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C244" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="D244" s="10">
+        <v>4</v>
+      </c>
+      <c r="E244" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F244" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G244" s="1"/>
+    </row>
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A245" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B245" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C245" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="D245" s="10">
+        <v>2</v>
+      </c>
+      <c r="E245" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F245" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G245" s="1"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A246" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B246" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C246" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D246" s="11">
+        <v>1</v>
+      </c>
+      <c r="E246" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F246" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G246" s="1"/>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A247" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B247" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="D247" s="11">
+        <v>2</v>
+      </c>
+      <c r="E247" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G247" s="1"/>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B248" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="D248" s="11">
+        <v>1</v>
+      </c>
+      <c r="E248" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F248" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G248" s="1"/>
+    </row>
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A249" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B249" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>470</v>
+      </c>
+      <c r="D249" s="11">
+        <v>1</v>
+      </c>
+      <c r="E249" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F249" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G249" s="1"/>
+    </row>
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B250" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="D250" s="11">
+        <v>2</v>
+      </c>
+      <c r="E250" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G250" s="1"/>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B251" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C251" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D251" s="11">
+        <v>1</v>
+      </c>
+      <c r="E251" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G251" s="1"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B252" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C252" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="D252" s="11">
+        <v>1</v>
+      </c>
+      <c r="E252" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G252" s="1"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B253" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C253" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="D253" s="11">
+        <v>1</v>
+      </c>
+      <c r="E253" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G253" s="1"/>
+    </row>
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A254" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B254" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C254" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D254" s="11">
+        <v>1</v>
+      </c>
+      <c r="E254" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G254" s="1"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B255" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D255" s="11">
+        <v>2</v>
+      </c>
+      <c r="E255" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G255" s="1"/>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A256" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B256" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C256" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="D256" s="11">
+        <v>1</v>
+      </c>
+      <c r="E256" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A257" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B257" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C257" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="D257" s="11">
+        <v>4</v>
+      </c>
+      <c r="E257" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A258" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B258" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D258" s="11">
+        <v>1</v>
+      </c>
+      <c r="E258" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G258" s="1"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G167:G170"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E73191-AC90-4686-8183-5D88761EF76F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B6F4D5-3448-4896-88F5-22708E996C23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B6F4D5-3448-4896-88F5-22708E996C23}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDE1A41-7419-4333-9382-5A27AF318B2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2068,14 +2068,14 @@
     <xf numFmtId="49" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2131,15 +2131,6 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2181,6 +2172,15 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="29" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2507,7 +2507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G259"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
@@ -2519,73 +2519,87 @@
     <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="21" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>9</v>
@@ -2594,21 +2608,21 @@
         <v>15</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="2">
-        <v>4</v>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3">
+        <v>9</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>9</v>
@@ -2616,65 +2630,65 @@
       <c r="F5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>28</v>
+      <c r="G5" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3">
         <v>12</v>
@@ -2686,21 +2700,21 @@
         <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>481</v>
       </c>
       <c r="D9" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>9</v>
@@ -2709,41 +2723,41 @@
         <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>481</v>
+        <v>26</v>
       </c>
       <c r="D10" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="D11" s="3">
         <v>4</v>
@@ -2752,24 +2766,24 @@
         <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>9</v>
@@ -2778,21 +2792,21 @@
         <v>15</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>9</v>
@@ -2801,67 +2815,67 @@
         <v>15</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>9</v>
@@ -2870,21 +2884,21 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D17" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>9</v>
@@ -2893,67 +2907,67 @@
         <v>15</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D18" s="3">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D19" s="3">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D20" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>9</v>
@@ -2962,21 +2976,21 @@
         <v>15</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D21" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>9</v>
@@ -2985,67 +2999,67 @@
         <v>15</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D22" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D23" s="3">
-        <v>17</v>
+        <v>82</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="3">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>9</v>
@@ -3054,21 +3068,21 @@
         <v>15</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D25" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>9</v>
@@ -3077,67 +3091,67 @@
         <v>15</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D26" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D28" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>9</v>
@@ -3146,21 +3160,21 @@
         <v>15</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D29" s="3">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>9</v>
@@ -3169,67 +3183,67 @@
         <v>15</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D30" s="3">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D31" s="3">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D32" s="3">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>9</v>
@@ -3238,21 +3252,21 @@
         <v>15</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D33" s="3">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>9</v>
@@ -3261,67 +3275,67 @@
         <v>15</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D34" s="3">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="D35" s="3">
-        <v>107</v>
+        <v>2</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>9</v>
@@ -3330,21 +3344,21 @@
         <v>15</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D37" s="3">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>9</v>
@@ -3353,67 +3367,67 @@
         <v>15</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D38" s="3">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D39" s="3">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>9</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D40" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>9</v>
@@ -3422,21 +3436,21 @@
         <v>15</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D41" s="3">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>9</v>
@@ -3445,21 +3459,21 @@
         <v>15</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D42" s="3">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>9</v>
@@ -3468,598 +3482,598 @@
         <v>15</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>99</v>
+      <c r="A43" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="D43" s="3">
-        <v>100</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>9</v>
+        <v>119</v>
+      </c>
+      <c r="E43" s="57" t="s">
+        <v>176</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D44" s="3">
-        <v>119</v>
-      </c>
-      <c r="E44" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D45" s="3">
-        <v>50</v>
-      </c>
-      <c r="E45" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>178</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D46" s="3">
-        <v>15</v>
-      </c>
-      <c r="E46" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D47" s="3">
-        <v>52</v>
-      </c>
-      <c r="E47" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D48" s="3">
-        <v>2</v>
-      </c>
-      <c r="E48" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="E48" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" s="3">
-        <v>6</v>
-      </c>
-      <c r="E49" s="60" t="s">
+        <v>85</v>
+      </c>
+      <c r="E49" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>160</v>
+        <v>482</v>
       </c>
       <c r="D50" s="3">
-        <v>85</v>
-      </c>
-      <c r="E50" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D51" s="3">
-        <v>55</v>
-      </c>
-      <c r="E51" s="60" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D52" s="3">
-        <v>119</v>
-      </c>
-      <c r="E52" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="E52" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D53" s="3">
         <v>2</v>
       </c>
-      <c r="E53" s="60" t="s">
+      <c r="E53" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>36</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>485</v>
+        <v>161</v>
       </c>
       <c r="D54" s="3">
-        <v>2</v>
-      </c>
-      <c r="E54" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D55" s="3">
-        <v>58</v>
-      </c>
-      <c r="E55" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="E55" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D56" s="3">
-        <v>1</v>
-      </c>
-      <c r="E56" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="E56" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D57" s="3">
-        <v>4</v>
-      </c>
-      <c r="E57" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="E57" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
-      </c>
-      <c r="E58" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E58" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D59" s="3">
-        <v>50</v>
-      </c>
-      <c r="E59" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D60" s="3">
-        <v>55</v>
-      </c>
-      <c r="E60" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="E60" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D61" s="3">
-        <v>53</v>
-      </c>
-      <c r="E61" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D62" s="3">
-        <v>19</v>
-      </c>
-      <c r="E62" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D63" s="3">
-        <v>4</v>
-      </c>
-      <c r="E63" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E63" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D64" s="3">
-        <v>70</v>
-      </c>
-      <c r="E64" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>132</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D65" s="3">
-        <v>14</v>
-      </c>
-      <c r="E65" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="E65" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>132</v>
+        <v>173</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D66" s="3">
-        <v>1</v>
-      </c>
-      <c r="E66" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="E66" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>174</v>
+        <v>179</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D67" s="3">
-        <v>49</v>
-      </c>
-      <c r="E67" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="E67" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>184</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D68" s="3">
         <v>1</v>
       </c>
-      <c r="E68" s="60" t="s">
+      <c r="E68" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F68" s="5" t="s">
@@ -4071,18 +4085,18 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D69" s="3">
         <v>1</v>
       </c>
-      <c r="E69" s="60" t="s">
+      <c r="E69" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F69" s="5" t="s">
@@ -4094,41 +4108,41 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D70" s="3">
         <v>1</v>
       </c>
-      <c r="E70" s="60" t="s">
+      <c r="E70" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D71" s="3">
         <v>1</v>
       </c>
-      <c r="E71" s="60" t="s">
+      <c r="E71" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F71" s="5" t="s">
@@ -4140,18 +4154,18 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D72" s="3">
         <v>1</v>
       </c>
-      <c r="E72" s="60" t="s">
+      <c r="E72" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F72" s="5" t="s">
@@ -4163,18 +4177,18 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D73" s="3">
         <v>1</v>
       </c>
-      <c r="E73" s="60" t="s">
+      <c r="E73" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F73" s="5" t="s">
@@ -4186,18 +4200,18 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D74" s="3">
         <v>1</v>
       </c>
-      <c r="E74" s="60" t="s">
+      <c r="E74" s="57" t="s">
         <v>176</v>
       </c>
       <c r="F74" s="5" t="s">
@@ -4208,26 +4222,26 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B75" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D75" s="3">
-        <v>1</v>
-      </c>
-      <c r="E75" s="60" t="s">
-        <v>176</v>
+      <c r="A75" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D75" s="10">
+        <v>3</v>
+      </c>
+      <c r="E75" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -4238,10 +4252,10 @@
         <v>199</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D76" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E76" s="44" t="s">
         <v>208</v>
@@ -4261,10 +4275,10 @@
         <v>199</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D77" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E77" s="44" t="s">
         <v>208</v>
@@ -4278,16 +4292,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B78" s="9" t="s">
         <v>199</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D78" s="10">
-        <v>5</v>
+        <v>204</v>
+      </c>
+      <c r="D78" s="11">
+        <v>30</v>
       </c>
       <c r="E78" s="44" t="s">
         <v>208</v>
@@ -4307,7 +4321,7 @@
         <v>199</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D79" s="11">
         <v>30</v>
@@ -4323,49 +4337,49 @@
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="D80" s="11">
-        <v>30</v>
-      </c>
-      <c r="E80" s="44" t="s">
+      <c r="A80" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>511</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D80" s="17">
+        <v>1</v>
+      </c>
+      <c r="E80" s="58" t="s">
         <v>208</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="3" t="s">
+      <c r="F80" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="18" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B81" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="D81" s="17">
-        <v>1</v>
-      </c>
-      <c r="E81" s="61" t="s">
-        <v>208</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" s="18" t="s">
-        <v>209</v>
+      <c r="A81" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="D81" s="10">
+        <v>2</v>
+      </c>
+      <c r="E81" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -4376,12 +4390,12 @@
         <v>228</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D82" s="10">
-        <v>2</v>
-      </c>
-      <c r="E82" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E82" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F82" s="5" t="s">
@@ -4399,12 +4413,12 @@
         <v>228</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D83" s="10">
-        <v>5</v>
-      </c>
-      <c r="E83" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="E83" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F83" s="5" t="s">
@@ -4416,18 +4430,18 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="16" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>228</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D84" s="10">
         <v>1</v>
       </c>
-      <c r="E84" s="62" t="s">
+      <c r="E84" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F84" s="5" t="s">
@@ -4439,18 +4453,18 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>228</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D85" s="10">
-        <v>1</v>
-      </c>
-      <c r="E85" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="E85" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F85" s="5" t="s">
@@ -4468,12 +4482,12 @@
         <v>228</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D86" s="10">
-        <v>2</v>
-      </c>
-      <c r="E86" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E86" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F86" s="5" t="s">
@@ -4491,12 +4505,12 @@
         <v>228</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D87" s="10">
-        <v>5</v>
-      </c>
-      <c r="E87" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="E87" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F87" s="5" t="s">
@@ -4514,12 +4528,12 @@
         <v>228</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D88" s="10">
-        <v>3</v>
-      </c>
-      <c r="E88" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="E88" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F88" s="5" t="s">
@@ -4537,12 +4551,12 @@
         <v>228</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D89" s="10">
         <v>1</v>
       </c>
-      <c r="E89" s="62" t="s">
+      <c r="E89" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F89" s="5" t="s">
@@ -4560,12 +4574,12 @@
         <v>228</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D90" s="10">
         <v>1</v>
       </c>
-      <c r="E90" s="62" t="s">
+      <c r="E90" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F90" s="5" t="s">
@@ -4583,12 +4597,12 @@
         <v>228</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D91" s="10">
-        <v>1</v>
-      </c>
-      <c r="E91" s="62" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F91" s="5" t="s">
@@ -4606,12 +4620,12 @@
         <v>228</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D92" s="10">
-        <v>6</v>
-      </c>
-      <c r="E92" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F92" s="5" t="s">
@@ -4629,12 +4643,12 @@
         <v>228</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D93" s="10">
-        <v>9</v>
-      </c>
-      <c r="E93" s="62" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F93" s="5" t="s">
@@ -4651,13 +4665,13 @@
       <c r="B94" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="D94" s="10">
-        <v>10</v>
-      </c>
-      <c r="E94" s="62" t="s">
+      <c r="C94" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="D94" s="11">
+        <v>2</v>
+      </c>
+      <c r="E94" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F94" s="5" t="s">
@@ -4675,12 +4689,12 @@
         <v>228</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D95" s="11">
-        <v>2</v>
-      </c>
-      <c r="E95" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E95" s="59" t="s">
         <v>210</v>
       </c>
       <c r="F95" s="5" t="s">
@@ -4691,49 +4705,49 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="16" t="s">
+      <c r="A96" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B96" s="19" t="s">
+      <c r="B96" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C96" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="D96" s="11">
-        <v>5</v>
-      </c>
-      <c r="E96" s="62" t="s">
+      <c r="C96" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" s="22">
+        <v>1</v>
+      </c>
+      <c r="E96" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="F96" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="3" t="s">
+      <c r="F96" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" s="18" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="B97" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="D97" s="22">
-        <v>1</v>
-      </c>
-      <c r="E97" s="63" t="s">
-        <v>210</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="18" t="s">
-        <v>231</v>
+      <c r="A97" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D97" s="10">
+        <v>10</v>
+      </c>
+      <c r="E97" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4744,12 +4758,12 @@
         <v>241</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D98" s="10">
         <v>10</v>
       </c>
-      <c r="E98" s="64" t="s">
+      <c r="E98" s="61" t="s">
         <v>232</v>
       </c>
       <c r="F98" s="5" t="s">
@@ -4761,18 +4775,18 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B99" s="23" t="s">
         <v>241</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D99" s="10">
-        <v>10</v>
-      </c>
-      <c r="E99" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="E99" s="61" t="s">
         <v>232</v>
       </c>
       <c r="F99" s="5" t="s">
@@ -4783,50 +4797,48 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="B100" s="23" t="s">
+      <c r="A100" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="B100" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D100" s="10">
-        <v>5</v>
-      </c>
-      <c r="E100" s="64" t="s">
+      <c r="C100" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="D100" s="22">
+        <v>7</v>
+      </c>
+      <c r="E100" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="F100" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" s="3" t="s">
+      <c r="F100" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100" s="18" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="B101" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="C101" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="D101" s="22">
-        <v>7</v>
-      </c>
-      <c r="E101" s="65" t="s">
-        <v>232</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G101" s="18" t="s">
-        <v>233</v>
-      </c>
+      <c r="A101" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="D101" s="10">
+        <v>2</v>
+      </c>
+      <c r="E101" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
@@ -4836,12 +4848,12 @@
         <v>248</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D102" s="10">
-        <v>2</v>
-      </c>
-      <c r="E102" s="66" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="63" t="s">
         <v>247</v>
       </c>
       <c r="F102" s="5" t="s">
@@ -4857,12 +4869,12 @@
         <v>248</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D103" s="10">
-        <v>9</v>
-      </c>
-      <c r="E103" s="66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="63" t="s">
         <v>247</v>
       </c>
       <c r="F103" s="5" t="s">
@@ -4871,46 +4883,46 @@
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="B104" s="25" t="s">
+      <c r="B104" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="D104" s="10">
-        <v>11</v>
-      </c>
-      <c r="E104" s="66" t="s">
+      <c r="C104" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="D104" s="22">
+        <v>4</v>
+      </c>
+      <c r="E104" s="64" t="s">
         <v>247</v>
       </c>
-      <c r="F104" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="1"/>
+      <c r="F104" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" s="27"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="20" t="s">
-        <v>242</v>
-      </c>
-      <c r="B105" s="26" t="s">
-        <v>248</v>
-      </c>
-      <c r="C105" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="D105" s="22">
-        <v>4</v>
-      </c>
-      <c r="E105" s="67" t="s">
-        <v>247</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="27"/>
+      <c r="A105" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="B105" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D105" s="10">
+        <v>34</v>
+      </c>
+      <c r="E105" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
@@ -4920,12 +4932,12 @@
         <v>258</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D106" s="10">
-        <v>34</v>
-      </c>
-      <c r="E106" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="E106" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F106" s="5" t="s">
@@ -4941,12 +4953,12 @@
         <v>258</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D107" s="10">
-        <v>2</v>
-      </c>
-      <c r="E107" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="E107" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F107" s="5" t="s">
@@ -4962,12 +4974,12 @@
         <v>258</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D108" s="10">
         <v>1</v>
       </c>
-      <c r="E108" s="68" t="s">
+      <c r="E108" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F108" s="5" t="s">
@@ -4983,12 +4995,12 @@
         <v>258</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D109" s="10">
         <v>1</v>
       </c>
-      <c r="E109" s="68" t="s">
+      <c r="E109" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F109" s="5" t="s">
@@ -5004,12 +5016,12 @@
         <v>258</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D110" s="10">
         <v>1</v>
       </c>
-      <c r="E110" s="68" t="s">
+      <c r="E110" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F110" s="5" t="s">
@@ -5025,12 +5037,12 @@
         <v>258</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D111" s="10">
-        <v>1</v>
-      </c>
-      <c r="E111" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" s="65" t="s">
         <v>249</v>
       </c>
       <c r="F111" s="5" t="s">
@@ -5039,46 +5051,46 @@
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="20" t="s">
         <v>258</v>
       </c>
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D112" s="10">
-        <v>22</v>
-      </c>
-      <c r="E112" s="68" t="s">
+      <c r="C112" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="D112" s="22">
+        <v>3</v>
+      </c>
+      <c r="E112" s="66" t="s">
         <v>249</v>
       </c>
-      <c r="F112" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" s="1"/>
+      <c r="F112" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="27"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="B113" s="29" t="s">
-        <v>258</v>
-      </c>
-      <c r="C113" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="D113" s="22">
+      <c r="A113" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D113" s="10">
         <v>3</v>
       </c>
-      <c r="E113" s="69" t="s">
-        <v>249</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G113" s="27"/>
+      <c r="E113" s="67" t="s">
+        <v>260</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" s="1"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
@@ -5088,12 +5100,12 @@
         <v>259</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D114" s="10">
-        <v>3</v>
-      </c>
-      <c r="E114" s="70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="67" t="s">
         <v>260</v>
       </c>
       <c r="F114" s="5" t="s">
@@ -5109,12 +5121,12 @@
         <v>259</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D115" s="10">
-        <v>9</v>
-      </c>
-      <c r="E115" s="70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" s="67" t="s">
         <v>260</v>
       </c>
       <c r="F115" s="5" t="s">
@@ -5130,12 +5142,12 @@
         <v>259</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D116" s="10">
-        <v>7</v>
-      </c>
-      <c r="E116" s="70" t="s">
+        <v>4</v>
+      </c>
+      <c r="E116" s="67" t="s">
         <v>260</v>
       </c>
       <c r="F116" s="5" t="s">
@@ -5151,12 +5163,12 @@
         <v>259</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D117" s="10">
-        <v>4</v>
-      </c>
-      <c r="E117" s="70" t="s">
+        <v>3</v>
+      </c>
+      <c r="E117" s="67" t="s">
         <v>260</v>
       </c>
       <c r="F117" s="5" t="s">
@@ -5172,12 +5184,12 @@
         <v>259</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D118" s="10">
-        <v>3</v>
-      </c>
-      <c r="E118" s="70" t="s">
+        <v>266</v>
+      </c>
+      <c r="D118" s="11">
+        <v>2</v>
+      </c>
+      <c r="E118" s="67" t="s">
         <v>260</v>
       </c>
       <c r="F118" s="5" t="s">
@@ -5187,19 +5199,19 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B119" s="16" t="s">
-        <v>259</v>
+        <v>274</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D119" s="11">
-        <v>2</v>
-      </c>
-      <c r="E119" s="70" t="s">
-        <v>260</v>
+        <v>268</v>
+      </c>
+      <c r="D119" s="10">
+        <v>4</v>
+      </c>
+      <c r="E119" s="36" t="s">
+        <v>273</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>15</v>
@@ -5208,18 +5220,18 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B120" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D120" s="10">
-        <v>4</v>
-      </c>
-      <c r="E120" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E120" s="36" t="s">
         <v>273</v>
       </c>
       <c r="F120" s="5" t="s">
@@ -5229,18 +5241,18 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B121" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D121" s="10">
-        <v>2</v>
-      </c>
-      <c r="E121" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E121" s="36" t="s">
         <v>273</v>
       </c>
       <c r="F121" s="5" t="s">
@@ -5250,18 +5262,18 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B122" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D122" s="10">
-        <v>3</v>
-      </c>
-      <c r="E122" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E122" s="36" t="s">
         <v>273</v>
       </c>
       <c r="F122" s="5" t="s">
@@ -5270,46 +5282,46 @@
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="B123" s="23" t="s">
+      <c r="A123" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="B123" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D123" s="10">
-        <v>2</v>
-      </c>
-      <c r="E123" s="37" t="s">
+      <c r="C123" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="D123" s="17">
+        <v>24</v>
+      </c>
+      <c r="E123" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="F123" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" s="1"/>
+      <c r="F123" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="27"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="B124" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C124" s="30" t="s">
-        <v>272</v>
-      </c>
-      <c r="D124" s="17">
-        <v>24</v>
-      </c>
-      <c r="E124" s="55" t="s">
-        <v>273</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" s="27"/>
+      <c r="A124" s="16" t="s">
+        <v>280</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D124" s="10">
+        <v>23</v>
+      </c>
+      <c r="E124" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
@@ -5319,12 +5331,12 @@
         <v>279</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D125" s="10">
-        <v>23</v>
-      </c>
-      <c r="E125" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="E125" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F125" s="5" t="s">
@@ -5340,12 +5352,12 @@
         <v>279</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D126" s="10">
         <v>4</v>
       </c>
-      <c r="E126" s="71" t="s">
+      <c r="E126" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F126" s="5" t="s">
@@ -5361,12 +5373,12 @@
         <v>279</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D127" s="10">
-        <v>4</v>
-      </c>
-      <c r="E127" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E127" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F127" s="5" t="s">
@@ -5382,12 +5394,12 @@
         <v>279</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D128" s="10">
-        <v>3</v>
-      </c>
-      <c r="E128" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="E128" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F128" s="5" t="s">
@@ -5403,12 +5415,12 @@
         <v>279</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D129" s="10">
-        <v>8</v>
-      </c>
-      <c r="E129" s="71" t="s">
+        <v>4</v>
+      </c>
+      <c r="E129" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F129" s="5" t="s">
@@ -5424,12 +5436,12 @@
         <v>279</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D130" s="10">
-        <v>4</v>
-      </c>
-      <c r="E130" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="E130" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F130" s="5" t="s">
@@ -5445,12 +5457,12 @@
         <v>279</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D131" s="10">
-        <v>2</v>
-      </c>
-      <c r="E131" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="E131" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F131" s="5" t="s">
@@ -5466,12 +5478,12 @@
         <v>279</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D132" s="10">
-        <v>1</v>
-      </c>
-      <c r="E132" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="E132" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F132" s="5" t="s">
@@ -5487,12 +5499,12 @@
         <v>279</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D133" s="10">
-        <v>25</v>
-      </c>
-      <c r="E133" s="71" t="s">
+        <v>2</v>
+      </c>
+      <c r="E133" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F133" s="5" t="s">
@@ -5508,12 +5520,12 @@
         <v>279</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D134" s="10">
         <v>2</v>
       </c>
-      <c r="E134" s="71" t="s">
+      <c r="E134" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F134" s="5" t="s">
@@ -5529,12 +5541,12 @@
         <v>279</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D135" s="10">
-        <v>2</v>
-      </c>
-      <c r="E135" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135" s="68" t="s">
         <v>294</v>
       </c>
       <c r="F135" s="5" t="s">
@@ -5543,56 +5555,56 @@
       <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="B136" s="31" t="s">
+      <c r="B136" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="C136" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="D136" s="10">
+      <c r="C136" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="D136" s="17">
         <v>1</v>
       </c>
-      <c r="E136" s="71" t="s">
+      <c r="E136" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="F136" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="1"/>
+      <c r="F136" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="27"/>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="20" t="s">
-        <v>280</v>
-      </c>
-      <c r="B137" s="32" t="s">
-        <v>279</v>
-      </c>
-      <c r="C137" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="D137" s="17">
-        <v>1</v>
-      </c>
-      <c r="E137" s="72" t="s">
-        <v>294</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G137" s="27"/>
+      <c r="A137" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="B137" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D137" s="10">
+        <v>20</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" s="1"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B138" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D138" s="10">
         <v>20</v>
@@ -5607,16 +5619,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D139" s="10">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>312</v>
@@ -5628,16 +5640,16 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B140" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D140" s="10">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>312</v>
@@ -5649,16 +5661,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B141" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D141" s="10">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>312</v>
@@ -5670,16 +5682,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B142" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D142" s="10">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>312</v>
@@ -5691,13 +5703,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B143" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D143" s="10">
         <v>20</v>
@@ -5711,82 +5723,84 @@
       <c r="G143" s="1"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="B144" s="33" t="s">
+      <c r="A144" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="B144" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="D144" s="10">
+      <c r="C144" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D144" s="17">
         <v>20</v>
       </c>
-      <c r="E144" s="3" t="s">
+      <c r="E144" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="F144" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G144" s="1"/>
+      <c r="F144" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="27"/>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="B145" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="C145" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="D145" s="17">
-        <v>20</v>
-      </c>
-      <c r="E145" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="27"/>
+      <c r="A145" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B145" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C145" s="38" t="s">
+        <v>314</v>
+      </c>
+      <c r="D145" s="38">
+        <v>12</v>
+      </c>
+      <c r="E145" s="36" t="s">
+        <v>344</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="2"/>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="16" t="s">
-        <v>342</v>
+      <c r="A146" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="B146" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="C146" s="36" t="s">
-        <v>314</v>
-      </c>
-      <c r="D146" s="36">
-        <v>12</v>
-      </c>
-      <c r="E146" s="37" t="s">
+      <c r="C146" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="D146" s="38">
+        <v>2</v>
+      </c>
+      <c r="E146" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="2"/>
+      <c r="G146" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="10" t="s">
-        <v>315</v>
+      <c r="A147" s="16" t="s">
+        <v>491</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="C147" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="D147" s="36">
-        <v>2</v>
-      </c>
-      <c r="E147" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="C147" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="D147" s="38">
+        <v>1</v>
+      </c>
+      <c r="E147" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F147" s="5" t="s">
@@ -5798,18 +5812,18 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="16" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B148" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="C148" s="36" t="s">
-        <v>316</v>
-      </c>
-      <c r="D148" s="36">
+      <c r="C148" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D148" s="38">
         <v>1</v>
       </c>
-      <c r="E148" s="37" t="s">
+      <c r="E148" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F148" s="5" t="s">
@@ -5821,18 +5835,18 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="16" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B149" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D149" s="36">
+        <v>318</v>
+      </c>
+      <c r="D149" s="38">
         <v>1</v>
       </c>
-      <c r="E149" s="37" t="s">
+      <c r="E149" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F149" s="5" t="s">
@@ -5844,18 +5858,18 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="16" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B150" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>318</v>
-      </c>
-      <c r="D150" s="36">
-        <v>1</v>
-      </c>
-      <c r="E150" s="37" t="s">
+        <v>319</v>
+      </c>
+      <c r="D150" s="10">
+        <v>2</v>
+      </c>
+      <c r="E150" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F150" s="5" t="s">
@@ -5867,41 +5881,41 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
-        <v>488</v>
+        <v>347</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D151" s="10">
-        <v>2</v>
-      </c>
-      <c r="E151" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E151" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B152" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D152" s="10">
         <v>1</v>
       </c>
-      <c r="E152" s="37" t="s">
+      <c r="E152" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F152" s="5" t="s">
@@ -5913,18 +5927,18 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="16" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B153" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D153" s="10">
         <v>1</v>
       </c>
-      <c r="E153" s="37" t="s">
+      <c r="E153" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F153" s="5" t="s">
@@ -5936,85 +5950,85 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
-        <v>349</v>
+        <v>499</v>
       </c>
       <c r="B154" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>322</v>
+        <v>500</v>
       </c>
       <c r="D154" s="10">
-        <v>1</v>
-      </c>
-      <c r="E154" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E154" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="F154" s="5"/>
       <c r="G154" s="2" t="s">
-        <v>367</v>
+        <v>501</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="16" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B155" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D155" s="10">
         <v>4</v>
       </c>
-      <c r="E155" s="37" t="s">
+      <c r="E155" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="F155" s="5"/>
-      <c r="G155" s="2" t="s">
-        <v>501</v>
+      <c r="F155" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="16" t="s">
-        <v>496</v>
+      <c r="A156" s="2" t="s">
+        <v>354</v>
       </c>
       <c r="B156" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>497</v>
+        <v>323</v>
       </c>
       <c r="D156" s="10">
-        <v>4</v>
-      </c>
-      <c r="E156" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E156" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G156" s="10" t="s">
-        <v>498</v>
+      <c r="G156" s="2" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B157" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D157" s="10">
         <v>1</v>
       </c>
-      <c r="E157" s="37" t="s">
+      <c r="E157" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F157" s="5" t="s">
@@ -6026,18 +6040,18 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B158" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D158" s="10">
         <v>1</v>
       </c>
-      <c r="E158" s="37" t="s">
+      <c r="E158" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F158" s="5" t="s">
@@ -6049,18 +6063,18 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B159" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D159" s="10">
         <v>1</v>
       </c>
-      <c r="E159" s="37" t="s">
+      <c r="E159" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F159" s="5" t="s">
@@ -6072,18 +6086,18 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B160" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D160" s="10">
         <v>1</v>
       </c>
-      <c r="E160" s="37" t="s">
+      <c r="E160" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F160" s="5" t="s">
@@ -6095,18 +6109,18 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B161" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D161" s="10">
         <v>1</v>
       </c>
-      <c r="E161" s="37" t="s">
+      <c r="E161" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F161" s="5" t="s">
@@ -6118,18 +6132,18 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B162" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D162" s="10">
         <v>1</v>
       </c>
-      <c r="E162" s="37" t="s">
+      <c r="E162" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F162" s="5" t="s">
@@ -6141,18 +6155,18 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B163" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D163" s="10">
         <v>1</v>
       </c>
-      <c r="E163" s="37" t="s">
+      <c r="E163" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F163" s="5" t="s">
@@ -6164,18 +6178,18 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B164" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D164" s="10">
         <v>1</v>
       </c>
-      <c r="E164" s="37" t="s">
+      <c r="E164" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F164" s="5" t="s">
@@ -6187,39 +6201,39 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>362</v>
+        <v>332</v>
       </c>
       <c r="B165" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D165" s="10">
-        <v>1</v>
-      </c>
-      <c r="E165" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="E165" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A166" s="2" t="s">
-        <v>332</v>
+        <v>368</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A166" s="10" t="s">
+        <v>363</v>
       </c>
       <c r="B166" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D166" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E166" s="37" t="s">
         <v>344</v>
@@ -6227,179 +6241,177 @@
       <c r="F166" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G166" s="2" t="s">
-        <v>368</v>
+      <c r="G166" s="71" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="167" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="10" t="s">
-        <v>363</v>
+      <c r="A167" s="2" t="s">
+        <v>364</v>
       </c>
       <c r="B167" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D167" s="10">
-        <v>1</v>
-      </c>
-      <c r="E167" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="E167" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G167" s="57" t="s">
-        <v>369</v>
-      </c>
+      <c r="G167" s="72"/>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B168" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D168" s="10">
-        <v>2</v>
-      </c>
-      <c r="E168" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E168" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G168" s="58"/>
+      <c r="G168" s="72"/>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B169" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D169" s="10">
-        <v>3</v>
-      </c>
-      <c r="E169" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E169" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G169" s="58"/>
+      <c r="G169" s="73"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="2" t="s">
-        <v>366</v>
+      <c r="A170" s="16" t="s">
+        <v>351</v>
       </c>
       <c r="B170" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D170" s="10">
         <v>1</v>
       </c>
-      <c r="E170" s="37" t="s">
+      <c r="E170" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G170" s="59"/>
+      <c r="G170" s="2" t="s">
+        <v>367</v>
+      </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="16" t="s">
-        <v>351</v>
+        <v>493</v>
       </c>
       <c r="B171" s="35" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>337</v>
+        <v>493</v>
       </c>
       <c r="D171" s="10">
-        <v>1</v>
-      </c>
-      <c r="E171" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E171" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>367</v>
+        <v>494</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B172" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D172" s="10">
-        <v>27</v>
-      </c>
-      <c r="E172" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E172" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="16" t="s">
-        <v>486</v>
+        <v>352</v>
       </c>
       <c r="B173" s="35" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>487</v>
+        <v>338</v>
       </c>
       <c r="D173" s="10">
-        <v>1</v>
-      </c>
-      <c r="E173" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="E173" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G173" s="2" t="s">
-        <v>492</v>
-      </c>
+      <c r="G173" s="2"/>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B174" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D174" s="10">
-        <v>2</v>
-      </c>
-      <c r="E174" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E174" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F174" s="5" t="s">
@@ -6409,18 +6421,18 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B175" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D175" s="10">
         <v>1</v>
       </c>
-      <c r="E175" s="37" t="s">
+      <c r="E175" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F175" s="5" t="s">
@@ -6430,60 +6442,62 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="16" t="s">
-        <v>355</v>
+        <v>495</v>
       </c>
       <c r="B176" s="35" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D176" s="10">
         <v>1</v>
       </c>
-      <c r="E176" s="37" t="s">
+      <c r="E176" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G176" s="2"/>
+      <c r="G176" s="2" t="s">
+        <v>345</v>
+      </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
-        <v>495</v>
+        <v>379</v>
       </c>
       <c r="B177" s="35" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
       <c r="D177" s="10">
-        <v>1</v>
-      </c>
-      <c r="E177" s="37" t="s">
-        <v>344</v>
+        <v>5</v>
+      </c>
+      <c r="E177" s="39" t="s">
+        <v>388</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>345</v>
+        <v>502</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B178" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D178" s="10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E178" s="39" t="s">
         <v>388</v>
@@ -6492,21 +6506,21 @@
         <v>15</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B179" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D179" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E179" s="39" t="s">
         <v>388</v>
@@ -6515,21 +6529,21 @@
         <v>15</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B180" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D180" s="10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E180" s="39" t="s">
         <v>388</v>
@@ -6538,21 +6552,21 @@
         <v>15</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B181" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D181" s="10">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E181" s="39" t="s">
         <v>388</v>
@@ -6561,21 +6575,21 @@
         <v>15</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B182" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D182" s="10">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E182" s="39" t="s">
         <v>388</v>
@@ -6584,21 +6598,21 @@
         <v>15</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B183" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D183" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E183" s="39" t="s">
         <v>388</v>
@@ -6607,21 +6621,21 @@
         <v>15</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B184" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D184" s="10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E184" s="39" t="s">
         <v>388</v>
@@ -6630,67 +6644,67 @@
         <v>15</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="16" t="s">
-        <v>386</v>
+      <c r="A185" s="20" t="s">
+        <v>387</v>
       </c>
       <c r="B185" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="C185" s="10" t="s">
-        <v>377</v>
-      </c>
-      <c r="D185" s="10">
-        <v>8</v>
-      </c>
-      <c r="E185" s="39" t="s">
+      <c r="C185" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="D185" s="17">
+        <v>7</v>
+      </c>
+      <c r="E185" s="40" t="s">
         <v>388</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="B186" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="C186" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="D186" s="17">
-        <v>7</v>
-      </c>
-      <c r="E186" s="40" t="s">
-        <v>388</v>
+      <c r="A186" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B186" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="D186" s="10">
+        <v>14</v>
+      </c>
+      <c r="E186" s="42" t="s">
+        <v>403</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G186" s="2" t="s">
-        <v>510</v>
+      <c r="G186" s="1" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B187" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D187" s="10">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E187" s="42" t="s">
         <v>403</v>
@@ -6699,18 +6713,18 @@
         <v>15</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B188" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D188" s="10">
         <v>4</v>
@@ -6722,21 +6736,21 @@
         <v>15</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B189" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D189" s="10">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E189" s="42" t="s">
         <v>403</v>
@@ -6745,21 +6759,21 @@
         <v>15</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B190" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D190" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E190" s="42" t="s">
         <v>403</v>
@@ -6768,21 +6782,21 @@
         <v>15</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B191" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D191" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E191" s="42" t="s">
         <v>403</v>
@@ -6791,21 +6805,21 @@
         <v>15</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B192" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D192" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" s="42" t="s">
         <v>403</v>
@@ -6814,21 +6828,21 @@
         <v>15</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B193" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D193" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E193" s="42" t="s">
         <v>403</v>
@@ -6837,21 +6851,21 @@
         <v>15</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B194" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D194" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E194" s="42" t="s">
         <v>403</v>
@@ -6865,16 +6879,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B195" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D195" s="10">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E195" s="42" t="s">
         <v>403</v>
@@ -6883,21 +6897,21 @@
         <v>15</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B196" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D196" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E196" s="42" t="s">
         <v>403</v>
@@ -6906,21 +6920,21 @@
         <v>15</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B197" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D197" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E197" s="42" t="s">
         <v>403</v>
@@ -6929,21 +6943,21 @@
         <v>15</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B198" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D198" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E198" s="42" t="s">
         <v>403</v>
@@ -6952,53 +6966,53 @@
         <v>15</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="B199" s="41" t="s">
-        <v>389</v>
+      <c r="A199" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="B199" s="70" t="s">
+        <v>556</v>
       </c>
       <c r="C199" s="10" t="s">
-        <v>402</v>
+        <v>555</v>
       </c>
       <c r="D199" s="10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E199" s="42" t="s">
-        <v>403</v>
+        <v>557</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>523</v>
+        <v>558</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="16" t="s">
-        <v>556</v>
-      </c>
-      <c r="B200" s="73" t="s">
-        <v>556</v>
+      <c r="A200" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" s="43" t="s">
+        <v>410</v>
       </c>
       <c r="C200" s="10" t="s">
-        <v>555</v>
+        <v>405</v>
       </c>
       <c r="D200" s="10">
-        <v>14</v>
-      </c>
-      <c r="E200" s="42" t="s">
-        <v>557</v>
+        <v>2</v>
+      </c>
+      <c r="E200" s="44" t="s">
+        <v>411</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>558</v>
+        <v>524</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7009,10 +7023,10 @@
         <v>410</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D201" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E201" s="44" t="s">
         <v>411</v>
@@ -7021,7 +7035,7 @@
         <v>15</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7032,10 +7046,10 @@
         <v>410</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D202" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E202" s="44" t="s">
         <v>411</v>
@@ -7044,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7054,10 +7068,10 @@
       <c r="B203" s="43" t="s">
         <v>410</v>
       </c>
-      <c r="C203" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="D203" s="10">
+      <c r="C203" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="D203" s="11">
         <v>1</v>
       </c>
       <c r="E203" s="44" t="s">
@@ -7067,7 +7081,7 @@
         <v>15</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7078,7 +7092,7 @@
         <v>410</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D204" s="11">
         <v>1</v>
@@ -7089,43 +7103,43 @@
       <c r="F204" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G204" s="1" t="s">
-        <v>532</v>
-      </c>
+      <c r="G204" s="1"/>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="B205" s="43" t="s">
-        <v>410</v>
-      </c>
-      <c r="C205" s="11" t="s">
-        <v>409</v>
-      </c>
-      <c r="D205" s="11">
-        <v>1</v>
-      </c>
-      <c r="E205" s="44" t="s">
-        <v>411</v>
+        <v>512</v>
+      </c>
+      <c r="B205" s="50" t="s">
+        <v>428</v>
+      </c>
+      <c r="C205" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="D205" s="10">
+        <v>4</v>
+      </c>
+      <c r="E205" s="51" t="s">
+        <v>435</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G205" s="1"/>
+      <c r="G205" s="1" t="s">
+        <v>547</v>
+      </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="B206" s="50" t="s">
-        <v>428</v>
+        <v>412</v>
+      </c>
+      <c r="B206" s="33" t="s">
+        <v>429</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D206" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E206" s="51" t="s">
         <v>435</v>
@@ -7134,21 +7148,21 @@
         <v>15</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B207" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="C207" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="D207" s="10">
-        <v>1</v>
+      <c r="B207" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C207" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="D207" s="11">
+        <v>2</v>
       </c>
       <c r="E207" s="51" t="s">
         <v>435</v>
@@ -7157,21 +7171,21 @@
         <v>15</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B208" s="49" t="s">
-        <v>430</v>
+      <c r="B208" s="45" t="s">
+        <v>433</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D208" s="11">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E208" s="51" t="s">
         <v>435</v>
@@ -7180,21 +7194,21 @@
         <v>15</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B209" s="45" t="s">
-        <v>433</v>
-      </c>
-      <c r="C209" s="11" t="s">
-        <v>416</v>
-      </c>
-      <c r="D209" s="11">
-        <v>10</v>
+      <c r="B209" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C209" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="D209" s="10">
+        <v>9</v>
       </c>
       <c r="E209" s="51" t="s">
         <v>435</v>
@@ -7203,7 +7217,7 @@
         <v>15</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7214,10 +7228,10 @@
         <v>429</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D210" s="10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E210" s="51" t="s">
         <v>435</v>
@@ -7237,10 +7251,10 @@
         <v>429</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D211" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E211" s="51" t="s">
         <v>435</v>
@@ -7249,7 +7263,7 @@
         <v>15</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7259,10 +7273,10 @@
       <c r="B212" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="C212" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="D212" s="10">
+      <c r="C212" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D212" s="11">
         <v>1</v>
       </c>
       <c r="E212" s="51" t="s">
@@ -7272,7 +7286,7 @@
         <v>15</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7283,7 +7297,7 @@
         <v>429</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D213" s="11">
         <v>1</v>
@@ -7295,21 +7309,21 @@
         <v>15</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B214" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="C214" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="D214" s="11">
-        <v>1</v>
+      <c r="B214" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="C214" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="D214" s="10">
+        <v>5</v>
       </c>
       <c r="E214" s="51" t="s">
         <v>435</v>
@@ -7318,7 +7332,7 @@
         <v>15</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7326,13 +7340,13 @@
         <v>412</v>
       </c>
       <c r="B215" s="45" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D215" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E215" s="51" t="s">
         <v>435</v>
@@ -7341,18 +7355,18 @@
         <v>15</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="45" t="s">
-        <v>429</v>
+      <c r="B216" s="49" t="s">
+        <v>430</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D216" s="10">
         <v>3</v>
@@ -7364,21 +7378,21 @@
         <v>15</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B217" s="49" t="s">
-        <v>430</v>
-      </c>
-      <c r="C217" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="D217" s="10">
-        <v>3</v>
+      <c r="B217" s="48" t="s">
+        <v>434</v>
+      </c>
+      <c r="C217" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="D217" s="11">
+        <v>2</v>
       </c>
       <c r="E217" s="51" t="s">
         <v>435</v>
@@ -7387,7 +7401,7 @@
         <v>15</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>526</v>
+        <v>552</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7398,10 +7412,10 @@
         <v>434</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D218" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" s="51" t="s">
         <v>435</v>
@@ -7410,21 +7424,21 @@
         <v>15</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B219" s="48" t="s">
-        <v>434</v>
+      <c r="B219" s="47" t="s">
+        <v>431</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D219" s="11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E219" s="51" t="s">
         <v>435</v>
@@ -7433,41 +7447,41 @@
         <v>15</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>412</v>
+        <v>445</v>
       </c>
       <c r="B220" s="47" t="s">
         <v>431</v>
       </c>
-      <c r="C220" s="11" t="s">
-        <v>427</v>
-      </c>
-      <c r="D220" s="11">
-        <v>10</v>
-      </c>
-      <c r="E220" s="51" t="s">
-        <v>435</v>
+      <c r="C220" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D220" s="10">
+        <v>2</v>
+      </c>
+      <c r="E220" s="46" t="s">
+        <v>444</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="B221" s="47" t="s">
-        <v>431</v>
+        <v>412</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>446</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D221" s="10">
         <v>2</v>
@@ -7479,7 +7493,7 @@
         <v>15</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7490,10 +7504,10 @@
         <v>446</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D222" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E222" s="46" t="s">
         <v>444</v>
@@ -7512,10 +7526,10 @@
       <c r="B223" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C223" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="D223" s="10">
+      <c r="C223" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="D223" s="11">
         <v>1</v>
       </c>
       <c r="E223" s="46" t="s">
@@ -7525,7 +7539,7 @@
         <v>15</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7535,8 +7549,8 @@
       <c r="B224" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C224" s="52" t="s">
-        <v>439</v>
+      <c r="C224" s="11" t="s">
+        <v>440</v>
       </c>
       <c r="D224" s="11">
         <v>1</v>
@@ -7548,21 +7562,21 @@
         <v>15</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B225" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="C225" s="11" t="s">
-        <v>440</v>
-      </c>
-      <c r="D225" s="11">
-        <v>1</v>
+      <c r="B225" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C225" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="D225" s="10">
+        <v>2</v>
       </c>
       <c r="E225" s="46" t="s">
         <v>444</v>
@@ -7571,18 +7585,18 @@
         <v>15</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B226" s="49" t="s">
-        <v>430</v>
+      <c r="B226" s="45" t="s">
+        <v>431</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D226" s="10">
         <v>2</v>
@@ -7594,99 +7608,99 @@
         <v>15</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="11" t="s">
+      <c r="A227" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="B227" s="45" t="s">
+      <c r="B227" s="53" t="s">
         <v>431</v>
       </c>
-      <c r="C227" s="10" t="s">
-        <v>442</v>
-      </c>
-      <c r="D227" s="10">
-        <v>2</v>
-      </c>
-      <c r="E227" s="46" t="s">
+      <c r="C227" s="17" t="s">
+        <v>443</v>
+      </c>
+      <c r="D227" s="17">
+        <v>3</v>
+      </c>
+      <c r="E227" s="54" t="s">
         <v>444</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G227" s="1" t="s">
-        <v>541</v>
+      <c r="G227" s="27" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="B228" s="53" t="s">
-        <v>431</v>
-      </c>
-      <c r="C228" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="D228" s="17">
-        <v>3</v>
-      </c>
-      <c r="E228" s="54" t="s">
-        <v>444</v>
+      <c r="A228" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="B228" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="C228" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="D228" s="10">
+        <v>5</v>
+      </c>
+      <c r="E228" s="36" t="s">
+        <v>447</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G228" s="27" t="s">
-        <v>542</v>
+      <c r="G228" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D229" s="10">
         <v>5</v>
       </c>
-      <c r="E229" s="37" t="s">
+      <c r="E229" s="36" t="s">
         <v>447</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D230" s="10">
-        <v>5</v>
-      </c>
-      <c r="E230" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E230" s="36" t="s">
         <v>447</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -7696,13 +7710,13 @@
       <c r="B231" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="C231" s="10" t="s">
-        <v>450</v>
-      </c>
-      <c r="D231" s="10">
+      <c r="C231" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D231" s="11">
         <v>1</v>
       </c>
-      <c r="E231" s="37" t="s">
+      <c r="E231" s="36" t="s">
         <v>447</v>
       </c>
       <c r="F231" s="5" t="s">
@@ -7713,49 +7727,49 @@
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="B232" s="11" t="s">
-        <v>432</v>
-      </c>
-      <c r="C232" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="D232" s="11">
+      <c r="A232" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="B232" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="C232" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="D232" s="22">
         <v>1</v>
       </c>
-      <c r="E232" s="37" t="s">
+      <c r="E232" s="55" t="s">
         <v>447</v>
       </c>
       <c r="F232" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G232" s="1" t="s">
-        <v>544</v>
+      <c r="G232" s="27" t="s">
+        <v>545</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="22" t="s">
-        <v>453</v>
-      </c>
-      <c r="B233" s="22" t="s">
-        <v>511</v>
-      </c>
-      <c r="C233" s="22" t="s">
-        <v>452</v>
-      </c>
-      <c r="D233" s="22">
-        <v>1</v>
-      </c>
-      <c r="E233" s="55" t="s">
-        <v>447</v>
+      <c r="A233" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B233" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C233" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D233" s="10">
+        <v>100</v>
+      </c>
+      <c r="E233" s="56" t="s">
+        <v>480</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G233" s="27" t="s">
-        <v>545</v>
+      <c r="G233" s="1" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -7766,10 +7780,10 @@
         <v>454</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D234" s="10">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E234" s="56" t="s">
         <v>480</v>
@@ -7777,9 +7791,7 @@
       <c r="F234" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G234" s="1" t="s">
-        <v>549</v>
-      </c>
+      <c r="G234" s="1"/>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
@@ -7789,10 +7801,10 @@
         <v>454</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D235" s="10">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="E235" s="56" t="s">
         <v>480</v>
@@ -7810,10 +7822,10 @@
         <v>454</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D236" s="10">
-        <v>69</v>
+        <v>16</v>
       </c>
       <c r="E236" s="56" t="s">
         <v>480</v>
@@ -7831,10 +7843,10 @@
         <v>454</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D237" s="10">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E237" s="56" t="s">
         <v>480</v>
@@ -7852,10 +7864,10 @@
         <v>454</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D238" s="10">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E238" s="56" t="s">
         <v>480</v>
@@ -7873,10 +7885,10 @@
         <v>454</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D239" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E239" s="56" t="s">
         <v>480</v>
@@ -7884,7 +7896,9 @@
       <c r="F239" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G239" s="1"/>
+      <c r="G239" s="1" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
@@ -7894,10 +7908,10 @@
         <v>454</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D240" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E240" s="56" t="s">
         <v>480</v>
@@ -7905,9 +7919,7 @@
       <c r="F240" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G240" s="1" t="s">
-        <v>554</v>
-      </c>
+      <c r="G240" s="1"/>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
@@ -7917,10 +7929,10 @@
         <v>454</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D241" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E241" s="56" t="s">
         <v>480</v>
@@ -7938,10 +7950,10 @@
         <v>454</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D242" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E242" s="56" t="s">
         <v>480</v>
@@ -7959,10 +7971,10 @@
         <v>454</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D243" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E243" s="56" t="s">
         <v>480</v>
@@ -7980,10 +7992,10 @@
         <v>454</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D244" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E244" s="56" t="s">
         <v>480</v>
@@ -8000,11 +8012,11 @@
       <c r="B245" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="C245" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="D245" s="10">
-        <v>2</v>
+      <c r="C245" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D245" s="11">
+        <v>1</v>
       </c>
       <c r="E245" s="56" t="s">
         <v>480</v>
@@ -8022,10 +8034,10 @@
         <v>454</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D246" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" s="56" t="s">
         <v>480</v>
@@ -8043,10 +8055,10 @@
         <v>454</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D247" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" s="56" t="s">
         <v>480</v>
@@ -8064,7 +8076,7 @@
         <v>454</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D248" s="11">
         <v>1</v>
@@ -8085,10 +8097,10 @@
         <v>454</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D249" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" s="56" t="s">
         <v>480</v>
@@ -8106,10 +8118,10 @@
         <v>454</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D250" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" s="56" t="s">
         <v>480</v>
@@ -8127,7 +8139,7 @@
         <v>454</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D251" s="11">
         <v>1</v>
@@ -8148,7 +8160,7 @@
         <v>454</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D252" s="11">
         <v>1</v>
@@ -8169,7 +8181,7 @@
         <v>454</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D253" s="11">
         <v>1</v>
@@ -8190,10 +8202,10 @@
         <v>454</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D254" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" s="56" t="s">
         <v>480</v>
@@ -8211,10 +8223,10 @@
         <v>454</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D255" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E255" s="56" t="s">
         <v>480</v>
@@ -8222,7 +8234,9 @@
       <c r="F255" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G255" s="1"/>
+      <c r="G255" s="1" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
@@ -8232,10 +8246,10 @@
         <v>454</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D256" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E256" s="56" t="s">
         <v>480</v>
@@ -8244,7 +8258,7 @@
         <v>15</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8255,10 +8269,10 @@
         <v>454</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D257" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E257" s="56" t="s">
         <v>480</v>
@@ -8266,44 +8280,18 @@
       <c r="F257" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G257" s="1" t="s">
-        <v>548</v>
-      </c>
+      <c r="G257" s="1"/>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A258" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="C258" s="11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D258" s="11">
-        <v>1</v>
-      </c>
-      <c r="E258" s="56" t="s">
-        <v>480</v>
-      </c>
-      <c r="F258" s="5" t="s">
-        <v>15</v>
-      </c>
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+      <c r="C258" s="1"/>
+      <c r="D258" s="1"/>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
       <c r="G258" s="1"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A259" s="1"/>
-      <c r="B259" s="1"/>
-      <c r="C259" s="1"/>
-      <c r="D259" s="1"/>
-      <c r="E259" s="1"/>
-      <c r="F259" s="1"/>
-      <c r="G259" s="1"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="G167:G170"/>
-  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andressluis\Desktop\Algoritmos_IPT\estoque_lab\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CDE1A41-7419-4333-9382-5A27AF318B2C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4638FBF4-E3BC-44CC-9867-0F39E257E70D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1469" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="561">
   <si>
     <t>Tipo</t>
   </si>
@@ -1702,6 +1702,12 @@
   </si>
   <si>
     <t>Slot da antena</t>
+  </si>
+  <si>
+    <t>COnector</t>
+  </si>
+  <si>
+    <t>BNC macho para KRE 2 vias</t>
   </si>
 </sst>
 </file>
@@ -2507,7 +2513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
@@ -4706,48 +4712,48 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="20" t="s">
+        <v>559</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="D96" s="22">
+        <v>2</v>
+      </c>
+      <c r="E96" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B97" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C96" s="20" t="s">
+      <c r="C97" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D96" s="22">
+      <c r="D97" s="22">
         <v>1</v>
       </c>
-      <c r="E96" s="60" t="s">
+      <c r="E97" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="18" t="s">
+      <c r="F97" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" s="18" t="s">
         <v>231</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A97" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="B97" s="23" t="s">
-        <v>241</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="D97" s="10">
-        <v>10</v>
-      </c>
-      <c r="E97" s="61" t="s">
-        <v>232</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -4758,7 +4764,7 @@
         <v>241</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D98" s="10">
         <v>10</v>
@@ -4775,16 +4781,16 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B99" s="23" t="s">
         <v>241</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D99" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E99" s="61" t="s">
         <v>232</v>
@@ -4797,48 +4803,50 @@
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A100" s="20" t="s">
+      <c r="A100" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="B100" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D100" s="10">
+        <v>5</v>
+      </c>
+      <c r="E100" s="61" t="s">
+        <v>232</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="B100" s="24" t="s">
+      <c r="B101" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="C100" s="22" t="s">
+      <c r="C101" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="D100" s="22">
+      <c r="D101" s="22">
         <v>7</v>
       </c>
-      <c r="E100" s="62" t="s">
+      <c r="E101" s="62" t="s">
         <v>232</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" s="18" t="s">
+      <c r="F101" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101" s="18" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A101" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="B101" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="C101" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="D101" s="10">
-        <v>2</v>
-      </c>
-      <c r="E101" s="63" t="s">
-        <v>247</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="16" t="s">
@@ -4848,10 +4856,10 @@
         <v>248</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D102" s="10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E102" s="63" t="s">
         <v>247</v>
@@ -4869,10 +4877,10 @@
         <v>248</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D103" s="10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E103" s="63" t="s">
         <v>247</v>
@@ -4883,46 +4891,46 @@
       <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="20" t="s">
+      <c r="A104" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="B104" s="26" t="s">
+      <c r="B104" s="25" t="s">
         <v>248</v>
       </c>
-      <c r="C104" s="22" t="s">
+      <c r="C104" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="D104" s="10">
+        <v>11</v>
+      </c>
+      <c r="E104" s="63" t="s">
+        <v>247</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" s="1"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="C105" s="22" t="s">
         <v>246</v>
       </c>
-      <c r="D104" s="22">
+      <c r="D105" s="22">
         <v>4</v>
       </c>
-      <c r="E104" s="64" t="s">
+      <c r="E105" s="64" t="s">
         <v>247</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="27"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A105" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="B105" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D105" s="10">
-        <v>34</v>
-      </c>
-      <c r="E105" s="65" t="s">
-        <v>249</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="1"/>
+      <c r="F105" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="27"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="16" t="s">
@@ -4932,10 +4940,10 @@
         <v>258</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D106" s="10">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E106" s="65" t="s">
         <v>249</v>
@@ -4953,10 +4961,10 @@
         <v>258</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D107" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="65" t="s">
         <v>249</v>
@@ -4974,7 +4982,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D108" s="10">
         <v>1</v>
@@ -4995,7 +5003,7 @@
         <v>258</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D109" s="10">
         <v>1</v>
@@ -5016,7 +5024,7 @@
         <v>258</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D110" s="10">
         <v>1</v>
@@ -5037,10 +5045,10 @@
         <v>258</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D111" s="10">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E111" s="65" t="s">
         <v>249</v>
@@ -5051,46 +5059,46 @@
       <c r="G111" s="1"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="20" t="s">
+      <c r="A112" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="B112" s="29" t="s">
+      <c r="B112" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="C112" s="18" t="s">
+      <c r="C112" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D112" s="10">
+        <v>22</v>
+      </c>
+      <c r="E112" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="1"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="B113" s="29" t="s">
+        <v>258</v>
+      </c>
+      <c r="C113" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="D112" s="22">
+      <c r="D113" s="22">
         <v>3</v>
       </c>
-      <c r="E112" s="66" t="s">
+      <c r="E113" s="66" t="s">
         <v>249</v>
       </c>
-      <c r="F112" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" s="27"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="B113" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D113" s="10">
-        <v>3</v>
-      </c>
-      <c r="E113" s="67" t="s">
-        <v>260</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G113" s="1"/>
+      <c r="F113" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" s="27"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="16" t="s">
@@ -5100,10 +5108,10 @@
         <v>259</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D114" s="10">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E114" s="67" t="s">
         <v>260</v>
@@ -5121,10 +5129,10 @@
         <v>259</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D115" s="10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E115" s="67" t="s">
         <v>260</v>
@@ -5142,10 +5150,10 @@
         <v>259</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D116" s="10">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E116" s="67" t="s">
         <v>260</v>
@@ -5163,10 +5171,10 @@
         <v>259</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D117" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E117" s="67" t="s">
         <v>260</v>
@@ -5184,10 +5192,10 @@
         <v>259</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D118" s="11">
-        <v>2</v>
+        <v>265</v>
+      </c>
+      <c r="D118" s="10">
+        <v>3</v>
       </c>
       <c r="E118" s="67" t="s">
         <v>260</v>
@@ -5199,19 +5207,19 @@
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B119" s="23" t="s">
-        <v>267</v>
+        <v>259</v>
+      </c>
+      <c r="B119" s="16" t="s">
+        <v>259</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D119" s="10">
-        <v>4</v>
-      </c>
-      <c r="E119" s="36" t="s">
-        <v>273</v>
+        <v>266</v>
+      </c>
+      <c r="D119" s="11">
+        <v>2</v>
+      </c>
+      <c r="E119" s="67" t="s">
+        <v>260</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>15</v>
@@ -5220,16 +5228,16 @@
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B120" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D120" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E120" s="36" t="s">
         <v>273</v>
@@ -5241,16 +5249,16 @@
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B121" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D121" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" s="36" t="s">
         <v>273</v>
@@ -5262,16 +5270,16 @@
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B122" s="23" t="s">
         <v>267</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D122" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" s="36" t="s">
         <v>273</v>
@@ -5282,46 +5290,46 @@
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A123" s="20" t="s">
+      <c r="A123" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D123" s="10">
+        <v>2</v>
+      </c>
+      <c r="E123" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G123" s="1"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="B123" s="24" t="s">
+      <c r="B124" s="24" t="s">
         <v>267</v>
       </c>
-      <c r="C123" s="30" t="s">
+      <c r="C124" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="D123" s="17">
+      <c r="D124" s="17">
         <v>24</v>
       </c>
-      <c r="E123" s="55" t="s">
+      <c r="E124" s="55" t="s">
         <v>273</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G123" s="27"/>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A124" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="B124" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="C124" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="D124" s="10">
-        <v>23</v>
-      </c>
-      <c r="E124" s="68" t="s">
-        <v>294</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" s="1"/>
+      <c r="F124" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G124" s="27"/>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="16" t="s">
@@ -5331,10 +5339,10 @@
         <v>279</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D125" s="10">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E125" s="68" t="s">
         <v>294</v>
@@ -5352,7 +5360,7 @@
         <v>279</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D126" s="10">
         <v>4</v>
@@ -5373,10 +5381,10 @@
         <v>279</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D127" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E127" s="68" t="s">
         <v>294</v>
@@ -5394,10 +5402,10 @@
         <v>279</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D128" s="10">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E128" s="68" t="s">
         <v>294</v>
@@ -5415,10 +5423,10 @@
         <v>279</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D129" s="10">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E129" s="68" t="s">
         <v>294</v>
@@ -5436,10 +5444,10 @@
         <v>279</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D130" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E130" s="68" t="s">
         <v>294</v>
@@ -5457,10 +5465,10 @@
         <v>279</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D131" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" s="68" t="s">
         <v>294</v>
@@ -5478,10 +5486,10 @@
         <v>279</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D132" s="10">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E132" s="68" t="s">
         <v>294</v>
@@ -5499,10 +5507,10 @@
         <v>279</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D133" s="10">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E133" s="68" t="s">
         <v>294</v>
@@ -5520,7 +5528,7 @@
         <v>279</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D134" s="10">
         <v>2</v>
@@ -5541,10 +5549,10 @@
         <v>279</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D135" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" s="68" t="s">
         <v>294</v>
@@ -5555,56 +5563,56 @@
       <c r="G135" s="1"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A136" s="20" t="s">
+      <c r="A136" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="B136" s="32" t="s">
+      <c r="B136" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="C136" s="14" t="s">
+      <c r="C136" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="D136" s="10">
+        <v>1</v>
+      </c>
+      <c r="E136" s="68" t="s">
+        <v>294</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="1"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C137" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="D136" s="17">
+      <c r="D137" s="17">
         <v>1</v>
       </c>
-      <c r="E136" s="69" t="s">
+      <c r="E137" s="69" t="s">
         <v>294</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="27"/>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A137" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="B137" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="D137" s="10">
-        <v>20</v>
-      </c>
-      <c r="E137" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G137" s="1"/>
+      <c r="F137" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" s="27"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B138" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C138" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D138" s="10">
         <v>20</v>
@@ -5619,16 +5627,16 @@
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B139" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D139" s="10">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>312</v>
@@ -5640,16 +5648,16 @@
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B140" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D140" s="10">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>312</v>
@@ -5661,16 +5669,16 @@
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="16" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B141" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D141" s="10">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>312</v>
@@ -5682,16 +5690,16 @@
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B142" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C142" s="8" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D142" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>312</v>
@@ -5703,13 +5711,13 @@
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="16" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B143" s="33" t="s">
         <v>295</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D143" s="10">
         <v>20</v>
@@ -5723,59 +5731,59 @@
       <c r="G143" s="1"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A144" s="20" t="s">
+      <c r="A144" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="B144" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D144" s="10">
+        <v>20</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="1"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="B144" s="34" t="s">
+      <c r="B145" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="14" t="s">
+      <c r="C145" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="D144" s="17">
+      <c r="D145" s="17">
         <v>20</v>
       </c>
-      <c r="E144" s="18" t="s">
+      <c r="E145" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="F144" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G144" s="27"/>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A145" s="16" t="s">
+      <c r="F145" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="27"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
         <v>342</v>
-      </c>
-      <c r="B145" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="C145" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="D145" s="38">
-        <v>12</v>
-      </c>
-      <c r="E145" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="2"/>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A146" s="10" t="s">
-        <v>315</v>
       </c>
       <c r="B146" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="C146" s="10" t="s">
-        <v>315</v>
+      <c r="C146" s="38" t="s">
+        <v>314</v>
       </c>
       <c r="D146" s="38">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E146" s="36" t="s">
         <v>344</v>
@@ -5783,22 +5791,20 @@
       <c r="F146" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G146" s="2" t="s">
-        <v>345</v>
-      </c>
+      <c r="G146" s="2"/>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="16" t="s">
-        <v>491</v>
+      <c r="A147" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="C147" s="38" t="s">
-        <v>316</v>
+        <v>313</v>
+      </c>
+      <c r="C147" s="10" t="s">
+        <v>315</v>
       </c>
       <c r="D147" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" s="36" t="s">
         <v>344</v>
@@ -5812,13 +5818,13 @@
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="16" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B148" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="C148" s="10" t="s">
-        <v>317</v>
+      <c r="C148" s="38" t="s">
+        <v>316</v>
       </c>
       <c r="D148" s="38">
         <v>1</v>
@@ -5835,13 +5841,13 @@
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B149" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D149" s="38">
         <v>1</v>
@@ -5858,16 +5864,16 @@
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="16" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B150" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="D150" s="10">
-        <v>2</v>
+        <v>318</v>
+      </c>
+      <c r="D150" s="38">
+        <v>1</v>
       </c>
       <c r="E150" s="36" t="s">
         <v>344</v>
@@ -5881,16 +5887,16 @@
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="16" t="s">
-        <v>347</v>
+        <v>488</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D151" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" s="36" t="s">
         <v>344</v>
@@ -5899,18 +5905,18 @@
         <v>15</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B152" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D152" s="10">
         <v>1</v>
@@ -5927,13 +5933,13 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B153" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D153" s="10">
         <v>1</v>
@@ -5950,34 +5956,36 @@
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="16" t="s">
-        <v>499</v>
+        <v>349</v>
       </c>
       <c r="B154" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>500</v>
+        <v>322</v>
       </c>
       <c r="D154" s="10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E154" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="F154" s="5"/>
+      <c r="F154" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="G154" s="2" t="s">
-        <v>501</v>
+        <v>367</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="16" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B155" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D155" s="10">
         <v>4</v>
@@ -5985,25 +5993,23 @@
       <c r="E155" s="36" t="s">
         <v>344</v>
       </c>
-      <c r="F155" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G155" s="10" t="s">
-        <v>498</v>
+      <c r="F155" s="5"/>
+      <c r="G155" s="2" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A156" s="2" t="s">
-        <v>354</v>
+      <c r="A156" s="16" t="s">
+        <v>496</v>
       </c>
       <c r="B156" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>323</v>
+        <v>497</v>
       </c>
       <c r="D156" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E156" s="36" t="s">
         <v>344</v>
@@ -6011,19 +6017,19 @@
       <c r="F156" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G156" s="2" t="s">
-        <v>367</v>
+      <c r="G156" s="10" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B157" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D157" s="10">
         <v>1</v>
@@ -6040,13 +6046,13 @@
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B158" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D158" s="10">
         <v>1</v>
@@ -6063,13 +6069,13 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B159" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D159" s="10">
         <v>1</v>
@@ -6086,13 +6092,13 @@
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B160" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D160" s="10">
         <v>1</v>
@@ -6109,13 +6115,13 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B161" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D161" s="10">
         <v>1</v>
@@ -6132,13 +6138,13 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B162" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D162" s="10">
         <v>1</v>
@@ -6155,13 +6161,13 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B163" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D163" s="10">
         <v>1</v>
@@ -6178,13 +6184,13 @@
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B164" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D164" s="10">
         <v>1</v>
@@ -6201,16 +6207,16 @@
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="B165" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D165" s="10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E165" s="36" t="s">
         <v>344</v>
@@ -6219,65 +6225,67 @@
         <v>15</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A166" s="10" t="s">
-        <v>363</v>
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="B166" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C166" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D166" s="10">
-        <v>1</v>
-      </c>
-      <c r="E166" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="E166" s="36" t="s">
         <v>344</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G166" s="71" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2" t="s">
-        <v>364</v>
+      <c r="G166" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A167" s="10" t="s">
+        <v>363</v>
       </c>
       <c r="B167" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C167" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D167" s="10">
-        <v>2</v>
-      </c>
-      <c r="E167" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="E167" s="37" t="s">
         <v>344</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G167" s="72"/>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G167" s="71" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B168" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D168" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E168" s="36" t="s">
         <v>344</v>
@@ -6289,16 +6297,16 @@
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B169" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C169" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D169" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E169" s="36" t="s">
         <v>344</v>
@@ -6306,17 +6314,17 @@
       <c r="F169" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G169" s="73"/>
+      <c r="G169" s="72"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A170" s="16" t="s">
-        <v>351</v>
+      <c r="A170" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="B170" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D170" s="10">
         <v>1</v>
@@ -6327,22 +6335,20 @@
       <c r="F170" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G170" s="2" t="s">
-        <v>367</v>
-      </c>
+      <c r="G170" s="73"/>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="16" t="s">
-        <v>493</v>
+        <v>351</v>
       </c>
       <c r="B171" s="35" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="C171" s="10" t="s">
-        <v>493</v>
+        <v>337</v>
       </c>
       <c r="D171" s="10">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E171" s="36" t="s">
         <v>344</v>
@@ -6351,21 +6357,21 @@
         <v>15</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>494</v>
+        <v>367</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="16" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B172" s="35" t="s">
         <v>346</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D172" s="10">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E172" s="36" t="s">
         <v>344</v>
@@ -6374,21 +6380,21 @@
         <v>15</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="16" t="s">
-        <v>352</v>
+        <v>486</v>
       </c>
       <c r="B173" s="35" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>338</v>
+        <v>487</v>
       </c>
       <c r="D173" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" s="36" t="s">
         <v>344</v>
@@ -6396,20 +6402,22 @@
       <c r="F173" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G173" s="2"/>
+      <c r="G173" s="2" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B174" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C174" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D174" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" s="36" t="s">
         <v>344</v>
@@ -6421,13 +6429,13 @@
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B175" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D175" s="10">
         <v>1</v>
@@ -6442,13 +6450,13 @@
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="16" t="s">
-        <v>495</v>
+        <v>355</v>
       </c>
       <c r="B176" s="35" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D176" s="10">
         <v>1</v>
@@ -6459,45 +6467,43 @@
       <c r="F176" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G176" s="2" t="s">
-        <v>345</v>
-      </c>
+      <c r="G176" s="2"/>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="16" t="s">
-        <v>379</v>
+        <v>495</v>
       </c>
       <c r="B177" s="35" t="s">
-        <v>313</v>
+        <v>346</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D177" s="10">
-        <v>5</v>
-      </c>
-      <c r="E177" s="39" t="s">
-        <v>388</v>
+        <v>1</v>
+      </c>
+      <c r="E177" s="36" t="s">
+        <v>344</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>502</v>
+        <v>345</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="16" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B178" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C178" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D178" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E178" s="39" t="s">
         <v>388</v>
@@ -6506,21 +6512,21 @@
         <v>15</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B179" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D179" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E179" s="39" t="s">
         <v>388</v>
@@ -6529,21 +6535,21 @@
         <v>15</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B180" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C180" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D180" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E180" s="39" t="s">
         <v>388</v>
@@ -6552,21 +6558,21 @@
         <v>15</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="16" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B181" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D181" s="10">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E181" s="39" t="s">
         <v>388</v>
@@ -6575,21 +6581,21 @@
         <v>15</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B182" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C182" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D182" s="10">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E182" s="39" t="s">
         <v>388</v>
@@ -6598,21 +6604,21 @@
         <v>15</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="16" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B183" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C183" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D183" s="10">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E183" s="39" t="s">
         <v>388</v>
@@ -6621,21 +6627,21 @@
         <v>15</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B184" s="35" t="s">
         <v>313</v>
       </c>
       <c r="C184" s="10" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D184" s="10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E184" s="39" t="s">
         <v>388</v>
@@ -6644,67 +6650,67 @@
         <v>15</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="20" t="s">
-        <v>387</v>
+      <c r="A185" s="16" t="s">
+        <v>386</v>
       </c>
       <c r="B185" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="C185" s="17" t="s">
+      <c r="C185" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="D185" s="10">
+        <v>8</v>
+      </c>
+      <c r="E185" s="39" t="s">
+        <v>388</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="B186" s="35" t="s">
+        <v>313</v>
+      </c>
+      <c r="C186" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="D185" s="17">
+      <c r="D186" s="17">
         <v>7</v>
       </c>
-      <c r="E185" s="40" t="s">
+      <c r="E186" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="F185" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G185" s="2" t="s">
+      <c r="F186" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="2" t="s">
         <v>510</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B186" s="41" t="s">
-        <v>389</v>
-      </c>
-      <c r="C186" s="10" t="s">
-        <v>390</v>
-      </c>
-      <c r="D186" s="10">
-        <v>14</v>
-      </c>
-      <c r="E186" s="42" t="s">
-        <v>403</v>
-      </c>
-      <c r="F186" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B187" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C187" s="10" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D187" s="10">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E187" s="42" t="s">
         <v>403</v>
@@ -6713,18 +6719,18 @@
         <v>15</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B188" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C188" s="10" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D188" s="10">
         <v>4</v>
@@ -6736,21 +6742,21 @@
         <v>15</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B189" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C189" s="10" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D189" s="10">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E189" s="42" t="s">
         <v>403</v>
@@ -6759,21 +6765,21 @@
         <v>15</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B190" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C190" s="10" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D190" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E190" s="42" t="s">
         <v>403</v>
@@ -6782,21 +6788,21 @@
         <v>15</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B191" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C191" s="10" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D191" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E191" s="42" t="s">
         <v>403</v>
@@ -6805,21 +6811,21 @@
         <v>15</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B192" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C192" s="10" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D192" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E192" s="42" t="s">
         <v>403</v>
@@ -6828,21 +6834,21 @@
         <v>15</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B193" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C193" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D193" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E193" s="42" t="s">
         <v>403</v>
@@ -6851,21 +6857,21 @@
         <v>15</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B194" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D194" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E194" s="42" t="s">
         <v>403</v>
@@ -6879,16 +6885,16 @@
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B195" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C195" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D195" s="10">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E195" s="42" t="s">
         <v>403</v>
@@ -6897,21 +6903,21 @@
         <v>15</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B196" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C196" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D196" s="10">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E196" s="42" t="s">
         <v>403</v>
@@ -6920,21 +6926,21 @@
         <v>15</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B197" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C197" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D197" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E197" s="42" t="s">
         <v>403</v>
@@ -6943,21 +6949,21 @@
         <v>15</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B198" s="41" t="s">
         <v>389</v>
       </c>
       <c r="C198" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D198" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E198" s="42" t="s">
         <v>403</v>
@@ -6966,53 +6972,53 @@
         <v>15</v>
       </c>
       <c r="G198" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" s="41" t="s">
+        <v>389</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D199" s="10">
+        <v>1</v>
+      </c>
+      <c r="E199" s="42" t="s">
+        <v>403</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G199" s="1" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A199" s="16" t="s">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="B199" s="70" t="s">
+      <c r="B200" s="70" t="s">
         <v>556</v>
       </c>
-      <c r="C199" s="10" t="s">
+      <c r="C200" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="D199" s="10">
+      <c r="D200" s="10">
         <v>14</v>
       </c>
-      <c r="E199" s="42" t="s">
+      <c r="E200" s="42" t="s">
         <v>557</v>
       </c>
-      <c r="F199" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G199" s="1" t="s">
+      <c r="F200" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G200" s="1" t="s">
         <v>558</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A200" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="B200" s="43" t="s">
-        <v>410</v>
-      </c>
-      <c r="C200" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="D200" s="10">
-        <v>2</v>
-      </c>
-      <c r="E200" s="44" t="s">
-        <v>411</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.25">
@@ -7023,10 +7029,10 @@
         <v>410</v>
       </c>
       <c r="C201" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D201" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E201" s="44" t="s">
         <v>411</v>
@@ -7035,7 +7041,7 @@
         <v>15</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.25">
@@ -7046,10 +7052,10 @@
         <v>410</v>
       </c>
       <c r="C202" s="10" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D202" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E202" s="44" t="s">
         <v>411</v>
@@ -7058,7 +7064,7 @@
         <v>15</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.25">
@@ -7068,10 +7074,10 @@
       <c r="B203" s="43" t="s">
         <v>410</v>
       </c>
-      <c r="C203" s="11" t="s">
-        <v>408</v>
-      </c>
-      <c r="D203" s="11">
+      <c r="C203" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D203" s="10">
         <v>1</v>
       </c>
       <c r="E203" s="44" t="s">
@@ -7081,7 +7087,7 @@
         <v>15</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.25">
@@ -7092,7 +7098,7 @@
         <v>410</v>
       </c>
       <c r="C204" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D204" s="11">
         <v>1</v>
@@ -7103,43 +7109,43 @@
       <c r="F204" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G204" s="1"/>
+      <c r="G204" s="1" t="s">
+        <v>532</v>
+      </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
-        <v>512</v>
-      </c>
-      <c r="B205" s="50" t="s">
-        <v>428</v>
-      </c>
-      <c r="C205" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="D205" s="10">
-        <v>4</v>
-      </c>
-      <c r="E205" s="51" t="s">
-        <v>435</v>
+        <v>404</v>
+      </c>
+      <c r="B205" s="43" t="s">
+        <v>410</v>
+      </c>
+      <c r="C205" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="D205" s="11">
+        <v>1</v>
+      </c>
+      <c r="E205" s="44" t="s">
+        <v>411</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G205" s="1" t="s">
-        <v>547</v>
-      </c>
+      <c r="G205" s="1"/>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="B206" s="33" t="s">
-        <v>429</v>
+        <v>512</v>
+      </c>
+      <c r="B206" s="50" t="s">
+        <v>428</v>
       </c>
       <c r="C206" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D206" s="10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E206" s="51" t="s">
         <v>435</v>
@@ -7148,21 +7154,21 @@
         <v>15</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B207" s="49" t="s">
-        <v>430</v>
-      </c>
-      <c r="C207" s="11" t="s">
-        <v>415</v>
-      </c>
-      <c r="D207" s="11">
-        <v>2</v>
+      <c r="B207" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C207" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D207" s="10">
+        <v>1</v>
       </c>
       <c r="E207" s="51" t="s">
         <v>435</v>
@@ -7171,21 +7177,21 @@
         <v>15</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B208" s="45" t="s">
-        <v>433</v>
+      <c r="B208" s="49" t="s">
+        <v>430</v>
       </c>
       <c r="C208" s="11" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D208" s="11">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E208" s="51" t="s">
         <v>435</v>
@@ -7194,21 +7200,21 @@
         <v>15</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B209" s="33" t="s">
-        <v>429</v>
-      </c>
-      <c r="C209" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="D209" s="10">
-        <v>9</v>
+      <c r="B209" s="45" t="s">
+        <v>433</v>
+      </c>
+      <c r="C209" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D209" s="11">
+        <v>10</v>
       </c>
       <c r="E209" s="51" t="s">
         <v>435</v>
@@ -7217,7 +7223,7 @@
         <v>15</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -7228,10 +7234,10 @@
         <v>429</v>
       </c>
       <c r="C210" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D210" s="10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E210" s="51" t="s">
         <v>435</v>
@@ -7251,10 +7257,10 @@
         <v>429</v>
       </c>
       <c r="C211" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D211" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E211" s="51" t="s">
         <v>435</v>
@@ -7263,7 +7269,7 @@
         <v>15</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -7273,10 +7279,10 @@
       <c r="B212" s="33" t="s">
         <v>429</v>
       </c>
-      <c r="C212" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="D212" s="11">
+      <c r="C212" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="D212" s="10">
         <v>1</v>
       </c>
       <c r="E212" s="51" t="s">
@@ -7286,7 +7292,7 @@
         <v>15</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -7297,7 +7303,7 @@
         <v>429</v>
       </c>
       <c r="C213" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D213" s="11">
         <v>1</v>
@@ -7309,21 +7315,21 @@
         <v>15</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B214" s="45" t="s">
-        <v>431</v>
-      </c>
-      <c r="C214" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="D214" s="10">
-        <v>5</v>
+      <c r="B214" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C214" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="D214" s="11">
+        <v>1</v>
       </c>
       <c r="E214" s="51" t="s">
         <v>435</v>
@@ -7332,7 +7338,7 @@
         <v>15</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -7340,13 +7346,13 @@
         <v>412</v>
       </c>
       <c r="B215" s="45" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C215" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D215" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E215" s="51" t="s">
         <v>435</v>
@@ -7355,18 +7361,18 @@
         <v>15</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B216" s="49" t="s">
-        <v>430</v>
+      <c r="B216" s="45" t="s">
+        <v>429</v>
       </c>
       <c r="C216" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D216" s="10">
         <v>3</v>
@@ -7378,21 +7384,21 @@
         <v>15</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B217" s="48" t="s">
-        <v>434</v>
-      </c>
-      <c r="C217" s="11" t="s">
-        <v>425</v>
-      </c>
-      <c r="D217" s="11">
-        <v>2</v>
+      <c r="B217" s="49" t="s">
+        <v>430</v>
+      </c>
+      <c r="C217" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="D217" s="10">
+        <v>3</v>
       </c>
       <c r="E217" s="51" t="s">
         <v>435</v>
@@ -7401,7 +7407,7 @@
         <v>15</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -7412,10 +7418,10 @@
         <v>434</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D218" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E218" s="51" t="s">
         <v>435</v>
@@ -7424,21 +7430,21 @@
         <v>15</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B219" s="47" t="s">
-        <v>431</v>
+      <c r="B219" s="48" t="s">
+        <v>434</v>
       </c>
       <c r="C219" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D219" s="11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E219" s="51" t="s">
         <v>435</v>
@@ -7447,41 +7453,41 @@
         <v>15</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="11" t="s">
-        <v>445</v>
+        <v>412</v>
       </c>
       <c r="B220" s="47" t="s">
         <v>431</v>
       </c>
-      <c r="C220" s="10" t="s">
-        <v>436</v>
-      </c>
-      <c r="D220" s="10">
-        <v>2</v>
-      </c>
-      <c r="E220" s="46" t="s">
-        <v>444</v>
+      <c r="C220" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="D220" s="11">
+        <v>10</v>
+      </c>
+      <c r="E220" s="51" t="s">
+        <v>435</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>529</v>
+        <v>551</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="11" t="s">
-        <v>412</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>446</v>
+        <v>445</v>
+      </c>
+      <c r="B221" s="47" t="s">
+        <v>431</v>
       </c>
       <c r="C221" s="10" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D221" s="10">
         <v>2</v>
@@ -7493,7 +7499,7 @@
         <v>15</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
@@ -7504,10 +7510,10 @@
         <v>446</v>
       </c>
       <c r="C222" s="10" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D222" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222" s="46" t="s">
         <v>444</v>
@@ -7526,10 +7532,10 @@
       <c r="B223" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C223" s="52" t="s">
-        <v>439</v>
-      </c>
-      <c r="D223" s="11">
+      <c r="C223" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D223" s="10">
         <v>1</v>
       </c>
       <c r="E223" s="46" t="s">
@@ -7539,7 +7545,7 @@
         <v>15</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -7549,8 +7555,8 @@
       <c r="B224" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="C224" s="11" t="s">
-        <v>440</v>
+      <c r="C224" s="52" t="s">
+        <v>439</v>
       </c>
       <c r="D224" s="11">
         <v>1</v>
@@ -7562,21 +7568,21 @@
         <v>15</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>530</v>
+        <v>537</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B225" s="49" t="s">
-        <v>430</v>
-      </c>
-      <c r="C225" s="10" t="s">
-        <v>441</v>
-      </c>
-      <c r="D225" s="10">
-        <v>2</v>
+      <c r="B225" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C225" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D225" s="11">
+        <v>1</v>
       </c>
       <c r="E225" s="46" t="s">
         <v>444</v>
@@ -7585,18 +7591,18 @@
         <v>15</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="B226" s="45" t="s">
-        <v>431</v>
+      <c r="B226" s="49" t="s">
+        <v>430</v>
       </c>
       <c r="C226" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D226" s="10">
         <v>2</v>
@@ -7608,64 +7614,64 @@
         <v>15</v>
       </c>
       <c r="G226" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="B227" s="45" t="s">
+        <v>431</v>
+      </c>
+      <c r="C227" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="D227" s="10">
+        <v>2</v>
+      </c>
+      <c r="E227" s="46" t="s">
+        <v>444</v>
+      </c>
+      <c r="F227" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" s="1" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="22" t="s">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="22" t="s">
         <v>412</v>
       </c>
-      <c r="B227" s="53" t="s">
+      <c r="B228" s="53" t="s">
         <v>431</v>
       </c>
-      <c r="C227" s="17" t="s">
+      <c r="C228" s="17" t="s">
         <v>443</v>
       </c>
-      <c r="D227" s="17">
+      <c r="D228" s="17">
         <v>3</v>
       </c>
-      <c r="E227" s="54" t="s">
+      <c r="E228" s="54" t="s">
         <v>444</v>
       </c>
-      <c r="F227" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G227" s="27" t="s">
+      <c r="F228" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" s="27" t="s">
         <v>542</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="11" t="s">
-        <v>448</v>
-      </c>
-      <c r="B228" s="11" t="s">
-        <v>448</v>
-      </c>
-      <c r="C228" s="10" t="s">
-        <v>448</v>
-      </c>
-      <c r="D228" s="10">
-        <v>5</v>
-      </c>
-      <c r="E228" s="36" t="s">
-        <v>447</v>
-      </c>
-      <c r="F228" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G228" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C229" s="10" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D229" s="10">
         <v>5</v>
@@ -7677,21 +7683,21 @@
         <v>15</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" s="11" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C230" s="10" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D230" s="10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E230" s="36" t="s">
         <v>447</v>
@@ -7700,7 +7706,7 @@
         <v>15</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -7710,10 +7716,10 @@
       <c r="B231" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="C231" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="D231" s="11">
+      <c r="C231" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D231" s="10">
         <v>1</v>
       </c>
       <c r="E231" s="36" t="s">
@@ -7727,49 +7733,49 @@
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A232" s="22" t="s">
+      <c r="A232" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="B232" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C232" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="D232" s="11">
+        <v>1</v>
+      </c>
+      <c r="E232" s="36" t="s">
+        <v>447</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="B232" s="22" t="s">
+      <c r="B233" s="22" t="s">
         <v>511</v>
       </c>
-      <c r="C232" s="22" t="s">
+      <c r="C233" s="22" t="s">
         <v>452</v>
       </c>
-      <c r="D232" s="22">
+      <c r="D233" s="22">
         <v>1</v>
       </c>
-      <c r="E232" s="55" t="s">
+      <c r="E233" s="55" t="s">
         <v>447</v>
       </c>
-      <c r="F232" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G232" s="27" t="s">
+      <c r="F233" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G233" s="27" t="s">
         <v>545</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A233" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="B233" s="11" t="s">
-        <v>454</v>
-      </c>
-      <c r="C233" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="D233" s="10">
-        <v>100</v>
-      </c>
-      <c r="E233" s="56" t="s">
-        <v>480</v>
-      </c>
-      <c r="F233" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G233" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -7780,10 +7786,10 @@
         <v>454</v>
       </c>
       <c r="C234" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D234" s="10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E234" s="56" t="s">
         <v>480</v>
@@ -7791,7 +7797,9 @@
       <c r="F234" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G234" s="1"/>
+      <c r="G234" s="1" t="s">
+        <v>549</v>
+      </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
@@ -7801,10 +7809,10 @@
         <v>454</v>
       </c>
       <c r="C235" s="10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D235" s="10">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="E235" s="56" t="s">
         <v>480</v>
@@ -7822,10 +7830,10 @@
         <v>454</v>
       </c>
       <c r="C236" s="10" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D236" s="10">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="E236" s="56" t="s">
         <v>480</v>
@@ -7843,10 +7851,10 @@
         <v>454</v>
       </c>
       <c r="C237" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D237" s="10">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E237" s="56" t="s">
         <v>480</v>
@@ -7864,10 +7872,10 @@
         <v>454</v>
       </c>
       <c r="C238" s="10" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D238" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E238" s="56" t="s">
         <v>480</v>
@@ -7885,10 +7893,10 @@
         <v>454</v>
       </c>
       <c r="C239" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D239" s="10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E239" s="56" t="s">
         <v>480</v>
@@ -7896,9 +7904,7 @@
       <c r="F239" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G239" s="1" t="s">
-        <v>554</v>
-      </c>
+      <c r="G239" s="1"/>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
@@ -7908,10 +7914,10 @@
         <v>454</v>
       </c>
       <c r="C240" s="10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D240" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E240" s="56" t="s">
         <v>480</v>
@@ -7919,7 +7925,9 @@
       <c r="F240" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G240" s="1"/>
+      <c r="G240" s="1" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
@@ -7929,10 +7937,10 @@
         <v>454</v>
       </c>
       <c r="C241" s="10" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D241" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E241" s="56" t="s">
         <v>480</v>
@@ -7950,10 +7958,10 @@
         <v>454</v>
       </c>
       <c r="C242" s="10" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D242" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E242" s="56" t="s">
         <v>480</v>
@@ -7971,10 +7979,10 @@
         <v>454</v>
       </c>
       <c r="C243" s="10" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D243" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E243" s="56" t="s">
         <v>480</v>
@@ -7992,10 +8000,10 @@
         <v>454</v>
       </c>
       <c r="C244" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D244" s="10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E244" s="56" t="s">
         <v>480</v>
@@ -8012,11 +8020,11 @@
       <c r="B245" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="C245" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="D245" s="11">
-        <v>1</v>
+      <c r="C245" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="D245" s="10">
+        <v>2</v>
       </c>
       <c r="E245" s="56" t="s">
         <v>480</v>
@@ -8034,10 +8042,10 @@
         <v>454</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D246" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246" s="56" t="s">
         <v>480</v>
@@ -8055,10 +8063,10 @@
         <v>454</v>
       </c>
       <c r="C247" s="11" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D247" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" s="56" t="s">
         <v>480</v>
@@ -8076,7 +8084,7 @@
         <v>454</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D248" s="11">
         <v>1</v>
@@ -8097,10 +8105,10 @@
         <v>454</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D249" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E249" s="56" t="s">
         <v>480</v>
@@ -8118,10 +8126,10 @@
         <v>454</v>
       </c>
       <c r="C250" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D250" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E250" s="56" t="s">
         <v>480</v>
@@ -8139,7 +8147,7 @@
         <v>454</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D251" s="11">
         <v>1</v>
@@ -8160,7 +8168,7 @@
         <v>454</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D252" s="11">
         <v>1</v>
@@ -8181,7 +8189,7 @@
         <v>454</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D253" s="11">
         <v>1</v>
@@ -8202,10 +8210,10 @@
         <v>454</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D254" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E254" s="56" t="s">
         <v>480</v>
@@ -8223,10 +8231,10 @@
         <v>454</v>
       </c>
       <c r="C255" s="11" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D255" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E255" s="56" t="s">
         <v>480</v>
@@ -8234,9 +8242,7 @@
       <c r="F255" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G255" s="1" t="s">
-        <v>546</v>
-      </c>
+      <c r="G255" s="1"/>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
@@ -8246,10 +8252,10 @@
         <v>454</v>
       </c>
       <c r="C256" s="11" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D256" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E256" s="56" t="s">
         <v>480</v>
@@ -8258,7 +8264,7 @@
         <v>15</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -8269,10 +8275,10 @@
         <v>454</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D257" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E257" s="56" t="s">
         <v>480</v>
@@ -8280,16 +8286,39 @@
       <c r="F257" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G257" s="1"/>
+      <c r="G257" s="1" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A258" s="1"/>
-      <c r="B258" s="1"/>
-      <c r="C258" s="1"/>
-      <c r="D258" s="1"/>
-      <c r="E258" s="1"/>
-      <c r="F258" s="1"/>
+      <c r="A258" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="B258" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C258" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="D258" s="11">
+        <v>1</v>
+      </c>
+      <c r="E258" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="F258" s="5" t="s">
+        <v>15</v>
+      </c>
       <c r="G258" s="1"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1"/>
+      <c r="D259" s="1"/>
+      <c r="E259" s="1"/>
+      <c r="F259" s="1"/>
+      <c r="G259" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10224,6 +10224,82 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Conector Bcn Femea X Femea</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Conector Rf</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>CONECTOR BNC FXF</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>4</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Maleta preta de conectores de RF</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>A Maleta Fica Na Mesa Branca</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>SLOT ÚNICO GERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Conector Kre X Bnc Macho</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Conector Rf</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>KRE X BNC MACHO</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>4</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Maleta Preta de conectores de RF</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>A Maleta</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>SLOT ÚNICO GERAL</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/planilhas/estoque_lab_completa.xlsx
+++ b/planilhas/estoque_lab_completa.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>480</v>
+        <v>960</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>235</v>
+        <v>470</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>410</v>
+        <v>820</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>550</v>
+        <v>1100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>490</v>
+        <v>980</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>285</v>
+        <v>570</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>180</v>
+        <v>360</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>535</v>
+        <v>1070</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>245</v>
+        <v>490</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>595</v>
+        <v>1190</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>260</v>
+        <v>520</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>425</v>
+        <v>850</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>275</v>
+        <v>550</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>595</v>
+        <v>1190</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>290</v>
+        <v>580</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>275</v>
+        <v>550</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>265</v>
+        <v>530</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>350</v>
+        <v>700</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>245</v>
+        <v>490</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>110</v>
+        <v>220</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>115</v>
+        <v>230</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>105</v>
+        <v>210</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>135</v>
+        <v>270</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -8382,7 +8382,7 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>460</v>
+        <v>920</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>345</v>
+        <v>690</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="E243" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="E246" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="E250" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="E252" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="E253" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         </is>
       </c>
       <c r="E257" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -10282,21 +10282,135 @@
         </is>
       </c>
       <c r="E260" t="n">
+        <v>8</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Maleta Preta de conectores de RF</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>A Maleta</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>SLOT ÚNICO GERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Conector N De Carga</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Conectores</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>CONECTOR N COM CARGA DE 50 Ω</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>2</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Maleta preta de conectores</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Mesa Branca</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>SLOT UNICO GERAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Conector Bnc T Fxfxm</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Conector Rf</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>BNT EM T FXFXM</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
         <v>4</v>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Maleta Preta de conectores de RF</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>A Maleta</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>SLOT ÚNICO GERAL</t>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Caixa dos conectores</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Armário</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>SLOT A</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Conector Bnc F 90º X Sma M</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Conector Rf</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>BNC F 90º X SMA M</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>4</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Caixa dos conectores</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Armário</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>SLOT A</t>
         </is>
       </c>
     </row>
